--- a/load-tests/load-test-report.xlsx
+++ b/load-tests/load-test-report.xlsx
@@ -444,7 +444,7 @@
         <v>Duration (seconds)</v>
       </c>
       <c r="B4">
-        <v>11.04</v>
+        <v>10.14</v>
       </c>
       <c r="C4" t="str">
         <v>Length of benchmarking</v>
@@ -455,7 +455,7 @@
         <v>Total Requests</v>
       </c>
       <c r="B5">
-        <v>49342</v>
+        <v>0</v>
       </c>
       <c r="C5" t="str">
         <v>Requests completed</v>
@@ -466,7 +466,7 @@
         <v>Average Requests / Sec</v>
       </c>
       <c r="B6">
-        <v>4486</v>
+        <v>0</v>
       </c>
       <c r="C6" t="str">
         <v>RPS throughput metric</v>
@@ -477,7 +477,7 @@
         <v>Total Bytes Transferred</v>
       </c>
       <c r="B7" t="str">
-        <v>47.76 MB</v>
+        <v>0.00 MB</v>
       </c>
       <c r="C7" t="str">
         <v>Total read bytes size</v>
@@ -488,7 +488,7 @@
         <v>Average Latency (ms)</v>
       </c>
       <c r="B8" t="str">
-        <v>21.77</v>
+        <v>0.00</v>
       </c>
       <c r="C8" t="str">
         <v>Average time to response</v>
@@ -499,7 +499,7 @@
         <v>Min Latency (ms)</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" t="str">
         <v>Fastest response time</v>
@@ -510,7 +510,7 @@
         <v>Max Latency (ms)</v>
       </c>
       <c r="B10">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="C10" t="str">
         <v>Slowest response time</v>
@@ -521,7 +521,7 @@
         <v>P99 Latency (ms)</v>
       </c>
       <c r="B11">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C11" t="str">
         <v>99th percentile response limit</v>
@@ -555,7 +555,7 @@
         <v>50% (Median)</v>
       </c>
       <c r="B2" t="str">
-        <v>17 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="3">
@@ -563,7 +563,7 @@
         <v>75%</v>
       </c>
       <c r="B3" t="str">
-        <v>30 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="4">
@@ -571,7 +571,7 @@
         <v>90%</v>
       </c>
       <c r="B4" t="str">
-        <v>46 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="5">
@@ -579,7 +579,7 @@
         <v>97.5%</v>
       </c>
       <c r="B5" t="str">
-        <v>66 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="6">
@@ -587,7 +587,7 @@
         <v>99%</v>
       </c>
       <c r="B6" t="str">
-        <v>80 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
     <row r="7">
@@ -595,7 +595,7 @@
         <v>99.9%</v>
       </c>
       <c r="B7" t="str">
-        <v>141 ms</v>
+        <v>0 ms</v>
       </c>
     </row>
   </sheetData>
@@ -652,7 +652,7 @@
         <v>GET</v>
       </c>
       <c r="D2">
-        <v>18.28</v>
+        <v>0</v>
       </c>
       <c r="E2" t="str">
         <v>200 OK</v>
@@ -675,7 +675,7 @@
         <v>GET</v>
       </c>
       <c r="D3">
-        <v>21.03</v>
+        <v>0</v>
       </c>
       <c r="E3" t="str">
         <v>200 OK</v>
@@ -698,7 +698,7 @@
         <v>GET</v>
       </c>
       <c r="D4">
-        <v>17.67</v>
+        <v>0</v>
       </c>
       <c r="E4" t="str">
         <v>200 OK</v>
@@ -721,7 +721,7 @@
         <v>GET</v>
       </c>
       <c r="D5">
-        <v>22.51</v>
+        <v>0</v>
       </c>
       <c r="E5" t="str">
         <v>200 OK</v>
@@ -744,7 +744,7 @@
         <v>GET</v>
       </c>
       <c r="D6">
-        <v>25.84</v>
+        <v>0</v>
       </c>
       <c r="E6" t="str">
         <v>200 OK</v>
@@ -767,7 +767,7 @@
         <v>GET</v>
       </c>
       <c r="D7">
-        <v>21.27</v>
+        <v>0</v>
       </c>
       <c r="E7" t="str">
         <v>200 OK</v>
@@ -790,7 +790,7 @@
         <v>GET</v>
       </c>
       <c r="D8">
-        <v>23.01</v>
+        <v>0</v>
       </c>
       <c r="E8" t="str">
         <v>200 OK</v>
@@ -813,7 +813,7 @@
         <v>GET</v>
       </c>
       <c r="D9">
-        <v>21.93</v>
+        <v>0</v>
       </c>
       <c r="E9" t="str">
         <v>200 OK</v>
@@ -836,7 +836,7 @@
         <v>GET</v>
       </c>
       <c r="D10">
-        <v>19.19</v>
+        <v>0</v>
       </c>
       <c r="E10" t="str">
         <v>200 OK</v>
@@ -859,7 +859,7 @@
         <v>GET</v>
       </c>
       <c r="D11">
-        <v>25.53</v>
+        <v>0</v>
       </c>
       <c r="E11" t="str">
         <v>200 OK</v>
@@ -882,7 +882,7 @@
         <v>GET</v>
       </c>
       <c r="D12">
-        <v>17.63</v>
+        <v>0</v>
       </c>
       <c r="E12" t="str">
         <v>200 OK</v>
@@ -905,7 +905,7 @@
         <v>GET</v>
       </c>
       <c r="D13">
-        <v>22.08</v>
+        <v>0</v>
       </c>
       <c r="E13" t="str">
         <v>200 OK</v>
@@ -928,7 +928,7 @@
         <v>GET</v>
       </c>
       <c r="D14">
-        <v>23.26</v>
+        <v>0</v>
       </c>
       <c r="E14" t="str">
         <v>200 OK</v>
@@ -951,7 +951,7 @@
         <v>GET</v>
       </c>
       <c r="D15">
-        <v>24.13</v>
+        <v>0</v>
       </c>
       <c r="E15" t="str">
         <v>200 OK</v>
@@ -974,7 +974,7 @@
         <v>GET</v>
       </c>
       <c r="D16">
-        <v>20.29</v>
+        <v>0</v>
       </c>
       <c r="E16" t="str">
         <v>200 OK</v>
@@ -997,7 +997,7 @@
         <v>GET</v>
       </c>
       <c r="D17">
-        <v>24.22</v>
+        <v>0</v>
       </c>
       <c r="E17" t="str">
         <v>200 OK</v>
@@ -1020,7 +1020,7 @@
         <v>GET</v>
       </c>
       <c r="D18">
-        <v>23.01</v>
+        <v>0</v>
       </c>
       <c r="E18" t="str">
         <v>200 OK</v>
@@ -1043,7 +1043,7 @@
         <v>GET</v>
       </c>
       <c r="D19">
-        <v>20.23</v>
+        <v>0</v>
       </c>
       <c r="E19" t="str">
         <v>200 OK</v>
@@ -1066,7 +1066,7 @@
         <v>GET</v>
       </c>
       <c r="D20">
-        <v>17.98</v>
+        <v>0</v>
       </c>
       <c r="E20" t="str">
         <v>200 OK</v>
@@ -1089,7 +1089,7 @@
         <v>GET</v>
       </c>
       <c r="D21">
-        <v>25.68</v>
+        <v>0</v>
       </c>
       <c r="E21" t="str">
         <v>200 OK</v>
@@ -1112,7 +1112,7 @@
         <v>GET</v>
       </c>
       <c r="D22">
-        <v>22.54</v>
+        <v>0</v>
       </c>
       <c r="E22" t="str">
         <v>200 OK</v>
@@ -1135,7 +1135,7 @@
         <v>GET</v>
       </c>
       <c r="D23">
-        <v>25.39</v>
+        <v>0</v>
       </c>
       <c r="E23" t="str">
         <v>200 OK</v>
@@ -1158,7 +1158,7 @@
         <v>GET</v>
       </c>
       <c r="D24">
-        <v>25.61</v>
+        <v>0</v>
       </c>
       <c r="E24" t="str">
         <v>200 OK</v>
@@ -1181,7 +1181,7 @@
         <v>GET</v>
       </c>
       <c r="D25">
-        <v>20.86</v>
+        <v>0</v>
       </c>
       <c r="E25" t="str">
         <v>200 OK</v>
@@ -1204,7 +1204,7 @@
         <v>GET</v>
       </c>
       <c r="D26">
-        <v>21.11</v>
+        <v>0</v>
       </c>
       <c r="E26" t="str">
         <v>200 OK</v>
@@ -1227,7 +1227,7 @@
         <v>GET</v>
       </c>
       <c r="D27">
-        <v>20.98</v>
+        <v>0</v>
       </c>
       <c r="E27" t="str">
         <v>200 OK</v>
@@ -1250,7 +1250,7 @@
         <v>GET</v>
       </c>
       <c r="D28">
-        <v>21.09</v>
+        <v>0</v>
       </c>
       <c r="E28" t="str">
         <v>200 OK</v>
@@ -1273,7 +1273,7 @@
         <v>GET</v>
       </c>
       <c r="D29">
-        <v>20.85</v>
+        <v>0</v>
       </c>
       <c r="E29" t="str">
         <v>200 OK</v>
@@ -1296,7 +1296,7 @@
         <v>GET</v>
       </c>
       <c r="D30">
-        <v>21.24</v>
+        <v>0</v>
       </c>
       <c r="E30" t="str">
         <v>200 OK</v>
@@ -1319,7 +1319,7 @@
         <v>GET</v>
       </c>
       <c r="D31">
-        <v>25.63</v>
+        <v>0</v>
       </c>
       <c r="E31" t="str">
         <v>200 OK</v>
@@ -1342,7 +1342,7 @@
         <v>GET</v>
       </c>
       <c r="D32">
-        <v>23.54</v>
+        <v>0</v>
       </c>
       <c r="E32" t="str">
         <v>200 OK</v>
@@ -1365,7 +1365,7 @@
         <v>GET</v>
       </c>
       <c r="D33">
-        <v>20.27</v>
+        <v>0</v>
       </c>
       <c r="E33" t="str">
         <v>200 OK</v>
@@ -1388,7 +1388,7 @@
         <v>GET</v>
       </c>
       <c r="D34">
-        <v>20.67</v>
+        <v>0</v>
       </c>
       <c r="E34" t="str">
         <v>200 OK</v>
@@ -1411,7 +1411,7 @@
         <v>GET</v>
       </c>
       <c r="D35">
-        <v>24.62</v>
+        <v>0</v>
       </c>
       <c r="E35" t="str">
         <v>200 OK</v>
@@ -1434,7 +1434,7 @@
         <v>GET</v>
       </c>
       <c r="D36">
-        <v>18.65</v>
+        <v>0</v>
       </c>
       <c r="E36" t="str">
         <v>200 OK</v>
@@ -1457,7 +1457,7 @@
         <v>GET</v>
       </c>
       <c r="D37">
-        <v>22.85</v>
+        <v>0</v>
       </c>
       <c r="E37" t="str">
         <v>200 OK</v>
@@ -1480,7 +1480,7 @@
         <v>GET</v>
       </c>
       <c r="D38">
-        <v>24.72</v>
+        <v>0</v>
       </c>
       <c r="E38" t="str">
         <v>200 OK</v>
@@ -1503,7 +1503,7 @@
         <v>GET</v>
       </c>
       <c r="D39">
-        <v>22.87</v>
+        <v>0</v>
       </c>
       <c r="E39" t="str">
         <v>200 OK</v>
@@ -1526,7 +1526,7 @@
         <v>GET</v>
       </c>
       <c r="D40">
-        <v>25.05</v>
+        <v>0</v>
       </c>
       <c r="E40" t="str">
         <v>200 OK</v>
@@ -1549,7 +1549,7 @@
         <v>GET</v>
       </c>
       <c r="D41">
-        <v>25.1</v>
+        <v>0</v>
       </c>
       <c r="E41" t="str">
         <v>200 OK</v>
@@ -1572,7 +1572,7 @@
         <v>GET</v>
       </c>
       <c r="D42">
-        <v>22.37</v>
+        <v>0</v>
       </c>
       <c r="E42" t="str">
         <v>200 OK</v>
@@ -1595,7 +1595,7 @@
         <v>GET</v>
       </c>
       <c r="D43">
-        <v>24.49</v>
+        <v>0</v>
       </c>
       <c r="E43" t="str">
         <v>200 OK</v>
@@ -1618,7 +1618,7 @@
         <v>GET</v>
       </c>
       <c r="D44">
-        <v>25.55</v>
+        <v>0</v>
       </c>
       <c r="E44" t="str">
         <v>200 OK</v>
@@ -1641,7 +1641,7 @@
         <v>GET</v>
       </c>
       <c r="D45">
-        <v>21.43</v>
+        <v>0</v>
       </c>
       <c r="E45" t="str">
         <v>200 OK</v>
@@ -1664,7 +1664,7 @@
         <v>GET</v>
       </c>
       <c r="D46">
-        <v>24.95</v>
+        <v>0</v>
       </c>
       <c r="E46" t="str">
         <v>200 OK</v>
@@ -1687,7 +1687,7 @@
         <v>GET</v>
       </c>
       <c r="D47">
-        <v>21.97</v>
+        <v>0</v>
       </c>
       <c r="E47" t="str">
         <v>200 OK</v>
@@ -1710,7 +1710,7 @@
         <v>GET</v>
       </c>
       <c r="D48">
-        <v>22.86</v>
+        <v>0</v>
       </c>
       <c r="E48" t="str">
         <v>200 OK</v>
@@ -1733,7 +1733,7 @@
         <v>GET</v>
       </c>
       <c r="D49">
-        <v>18.27</v>
+        <v>0</v>
       </c>
       <c r="E49" t="str">
         <v>200 OK</v>
@@ -1756,7 +1756,7 @@
         <v>GET</v>
       </c>
       <c r="D50">
-        <v>21.72</v>
+        <v>0</v>
       </c>
       <c r="E50" t="str">
         <v>200 OK</v>
@@ -1779,7 +1779,7 @@
         <v>GET</v>
       </c>
       <c r="D51">
-        <v>21.62</v>
+        <v>0</v>
       </c>
       <c r="E51" t="str">
         <v>200 OK</v>
@@ -1802,7 +1802,7 @@
         <v>GET</v>
       </c>
       <c r="D52">
-        <v>19.44</v>
+        <v>0</v>
       </c>
       <c r="E52" t="str">
         <v>200 OK</v>
@@ -1825,7 +1825,7 @@
         <v>GET</v>
       </c>
       <c r="D53">
-        <v>23.89</v>
+        <v>0</v>
       </c>
       <c r="E53" t="str">
         <v>200 OK</v>
@@ -1848,7 +1848,7 @@
         <v>GET</v>
       </c>
       <c r="D54">
-        <v>25.45</v>
+        <v>0</v>
       </c>
       <c r="E54" t="str">
         <v>200 OK</v>
@@ -1871,7 +1871,7 @@
         <v>GET</v>
       </c>
       <c r="D55">
-        <v>25.19</v>
+        <v>0</v>
       </c>
       <c r="E55" t="str">
         <v>200 OK</v>
@@ -1894,7 +1894,7 @@
         <v>GET</v>
       </c>
       <c r="D56">
-        <v>25.07</v>
+        <v>0</v>
       </c>
       <c r="E56" t="str">
         <v>200 OK</v>
@@ -1917,7 +1917,7 @@
         <v>GET</v>
       </c>
       <c r="D57">
-        <v>25.74</v>
+        <v>0</v>
       </c>
       <c r="E57" t="str">
         <v>200 OK</v>
@@ -1940,7 +1940,7 @@
         <v>GET</v>
       </c>
       <c r="D58">
-        <v>17.74</v>
+        <v>0</v>
       </c>
       <c r="E58" t="str">
         <v>200 OK</v>
@@ -1963,7 +1963,7 @@
         <v>GET</v>
       </c>
       <c r="D59">
-        <v>20.09</v>
+        <v>0</v>
       </c>
       <c r="E59" t="str">
         <v>200 OK</v>
@@ -1986,7 +1986,7 @@
         <v>GET</v>
       </c>
       <c r="D60">
-        <v>22.44</v>
+        <v>0</v>
       </c>
       <c r="E60" t="str">
         <v>200 OK</v>
@@ -2009,7 +2009,7 @@
         <v>GET</v>
       </c>
       <c r="D61">
-        <v>23.83</v>
+        <v>0</v>
       </c>
       <c r="E61" t="str">
         <v>200 OK</v>
@@ -2032,7 +2032,7 @@
         <v>GET</v>
       </c>
       <c r="D62">
-        <v>24.58</v>
+        <v>0</v>
       </c>
       <c r="E62" t="str">
         <v>200 OK</v>
@@ -2055,7 +2055,7 @@
         <v>GET</v>
       </c>
       <c r="D63">
-        <v>21.85</v>
+        <v>0</v>
       </c>
       <c r="E63" t="str">
         <v>200 OK</v>
@@ -2078,7 +2078,7 @@
         <v>GET</v>
       </c>
       <c r="D64">
-        <v>22.94</v>
+        <v>0</v>
       </c>
       <c r="E64" t="str">
         <v>200 OK</v>
@@ -2101,7 +2101,7 @@
         <v>GET</v>
       </c>
       <c r="D65">
-        <v>24.57</v>
+        <v>0</v>
       </c>
       <c r="E65" t="str">
         <v>200 OK</v>
@@ -2124,7 +2124,7 @@
         <v>GET</v>
       </c>
       <c r="D66">
-        <v>17.94</v>
+        <v>0</v>
       </c>
       <c r="E66" t="str">
         <v>200 OK</v>
@@ -2147,7 +2147,7 @@
         <v>GET</v>
       </c>
       <c r="D67">
-        <v>25.39</v>
+        <v>0</v>
       </c>
       <c r="E67" t="str">
         <v>200 OK</v>
@@ -2170,7 +2170,7 @@
         <v>GET</v>
       </c>
       <c r="D68">
-        <v>19.17</v>
+        <v>0</v>
       </c>
       <c r="E68" t="str">
         <v>200 OK</v>
@@ -2193,7 +2193,7 @@
         <v>GET</v>
       </c>
       <c r="D69">
-        <v>24.61</v>
+        <v>0</v>
       </c>
       <c r="E69" t="str">
         <v>200 OK</v>
@@ -2216,7 +2216,7 @@
         <v>GET</v>
       </c>
       <c r="D70">
-        <v>21.42</v>
+        <v>0</v>
       </c>
       <c r="E70" t="str">
         <v>200 OK</v>
@@ -2239,7 +2239,7 @@
         <v>GET</v>
       </c>
       <c r="D71">
-        <v>19.66</v>
+        <v>0</v>
       </c>
       <c r="E71" t="str">
         <v>200 OK</v>
@@ -2262,7 +2262,7 @@
         <v>GET</v>
       </c>
       <c r="D72">
-        <v>23.54</v>
+        <v>0</v>
       </c>
       <c r="E72" t="str">
         <v>200 OK</v>
@@ -2285,7 +2285,7 @@
         <v>GET</v>
       </c>
       <c r="D73">
-        <v>21.18</v>
+        <v>0</v>
       </c>
       <c r="E73" t="str">
         <v>200 OK</v>
@@ -2308,7 +2308,7 @@
         <v>GET</v>
       </c>
       <c r="D74">
-        <v>23.86</v>
+        <v>0</v>
       </c>
       <c r="E74" t="str">
         <v>200 OK</v>
@@ -2331,7 +2331,7 @@
         <v>GET</v>
       </c>
       <c r="D75">
-        <v>24.15</v>
+        <v>0</v>
       </c>
       <c r="E75" t="str">
         <v>200 OK</v>
@@ -2354,7 +2354,7 @@
         <v>GET</v>
       </c>
       <c r="D76">
-        <v>19.52</v>
+        <v>0</v>
       </c>
       <c r="E76" t="str">
         <v>200 OK</v>
@@ -2377,7 +2377,7 @@
         <v>GET</v>
       </c>
       <c r="D77">
-        <v>20.44</v>
+        <v>0</v>
       </c>
       <c r="E77" t="str">
         <v>200 OK</v>
@@ -2400,7 +2400,7 @@
         <v>GET</v>
       </c>
       <c r="D78">
-        <v>17.83</v>
+        <v>0</v>
       </c>
       <c r="E78" t="str">
         <v>200 OK</v>
@@ -2423,7 +2423,7 @@
         <v>GET</v>
       </c>
       <c r="D79">
-        <v>24.1</v>
+        <v>0</v>
       </c>
       <c r="E79" t="str">
         <v>200 OK</v>
@@ -2446,7 +2446,7 @@
         <v>GET</v>
       </c>
       <c r="D80">
-        <v>22.16</v>
+        <v>0</v>
       </c>
       <c r="E80" t="str">
         <v>200 OK</v>
@@ -2469,7 +2469,7 @@
         <v>GET</v>
       </c>
       <c r="D81">
-        <v>18.73</v>
+        <v>0</v>
       </c>
       <c r="E81" t="str">
         <v>200 OK</v>
@@ -2492,7 +2492,7 @@
         <v>GET</v>
       </c>
       <c r="D82">
-        <v>22.63</v>
+        <v>0</v>
       </c>
       <c r="E82" t="str">
         <v>200 OK</v>
@@ -2515,7 +2515,7 @@
         <v>GET</v>
       </c>
       <c r="D83">
-        <v>21.92</v>
+        <v>0</v>
       </c>
       <c r="E83" t="str">
         <v>200 OK</v>
@@ -2538,7 +2538,7 @@
         <v>GET</v>
       </c>
       <c r="D84">
-        <v>20.29</v>
+        <v>0</v>
       </c>
       <c r="E84" t="str">
         <v>200 OK</v>
@@ -2561,7 +2561,7 @@
         <v>GET</v>
       </c>
       <c r="D85">
-        <v>23.69</v>
+        <v>0</v>
       </c>
       <c r="E85" t="str">
         <v>200 OK</v>
@@ -2584,7 +2584,7 @@
         <v>GET</v>
       </c>
       <c r="D86">
-        <v>20.4</v>
+        <v>0</v>
       </c>
       <c r="E86" t="str">
         <v>200 OK</v>
@@ -2607,7 +2607,7 @@
         <v>GET</v>
       </c>
       <c r="D87">
-        <v>25.3</v>
+        <v>0</v>
       </c>
       <c r="E87" t="str">
         <v>200 OK</v>
@@ -2630,7 +2630,7 @@
         <v>GET</v>
       </c>
       <c r="D88">
-        <v>18.13</v>
+        <v>0</v>
       </c>
       <c r="E88" t="str">
         <v>200 OK</v>
@@ -2653,7 +2653,7 @@
         <v>GET</v>
       </c>
       <c r="D89">
-        <v>23.2</v>
+        <v>0</v>
       </c>
       <c r="E89" t="str">
         <v>200 OK</v>
@@ -2676,7 +2676,7 @@
         <v>GET</v>
       </c>
       <c r="D90">
-        <v>20.59</v>
+        <v>0</v>
       </c>
       <c r="E90" t="str">
         <v>200 OK</v>
@@ -2699,7 +2699,7 @@
         <v>GET</v>
       </c>
       <c r="D91">
-        <v>19.81</v>
+        <v>0</v>
       </c>
       <c r="E91" t="str">
         <v>200 OK</v>
@@ -2722,7 +2722,7 @@
         <v>GET</v>
       </c>
       <c r="D92">
-        <v>20.51</v>
+        <v>0</v>
       </c>
       <c r="E92" t="str">
         <v>200 OK</v>
@@ -2745,7 +2745,7 @@
         <v>GET</v>
       </c>
       <c r="D93">
-        <v>25.63</v>
+        <v>0</v>
       </c>
       <c r="E93" t="str">
         <v>200 OK</v>
@@ -2768,7 +2768,7 @@
         <v>GET</v>
       </c>
       <c r="D94">
-        <v>18.87</v>
+        <v>0</v>
       </c>
       <c r="E94" t="str">
         <v>200 OK</v>
@@ -2791,7 +2791,7 @@
         <v>GET</v>
       </c>
       <c r="D95">
-        <v>18.43</v>
+        <v>0</v>
       </c>
       <c r="E95" t="str">
         <v>200 OK</v>
@@ -2814,7 +2814,7 @@
         <v>GET</v>
       </c>
       <c r="D96">
-        <v>22.9</v>
+        <v>0</v>
       </c>
       <c r="E96" t="str">
         <v>200 OK</v>
@@ -2837,7 +2837,7 @@
         <v>GET</v>
       </c>
       <c r="D97">
-        <v>18.54</v>
+        <v>0</v>
       </c>
       <c r="E97" t="str">
         <v>200 OK</v>
@@ -2860,7 +2860,7 @@
         <v>GET</v>
       </c>
       <c r="D98">
-        <v>20.34</v>
+        <v>0</v>
       </c>
       <c r="E98" t="str">
         <v>200 OK</v>
@@ -2883,7 +2883,7 @@
         <v>GET</v>
       </c>
       <c r="D99">
-        <v>24.61</v>
+        <v>0</v>
       </c>
       <c r="E99" t="str">
         <v>200 OK</v>
@@ -2906,7 +2906,7 @@
         <v>GET</v>
       </c>
       <c r="D100">
-        <v>24.14</v>
+        <v>0</v>
       </c>
       <c r="E100" t="str">
         <v>200 OK</v>
@@ -2929,7 +2929,7 @@
         <v>GET</v>
       </c>
       <c r="D101">
-        <v>20.44</v>
+        <v>0</v>
       </c>
       <c r="E101" t="str">
         <v>200 OK</v>
@@ -2952,7 +2952,7 @@
         <v>GET</v>
       </c>
       <c r="D102">
-        <v>21.61</v>
+        <v>0</v>
       </c>
       <c r="E102" t="str">
         <v>200 OK</v>
@@ -2975,7 +2975,7 @@
         <v>GET</v>
       </c>
       <c r="D103">
-        <v>25.42</v>
+        <v>0</v>
       </c>
       <c r="E103" t="str">
         <v>200 OK</v>
@@ -2998,7 +2998,7 @@
         <v>GET</v>
       </c>
       <c r="D104">
-        <v>22.31</v>
+        <v>0</v>
       </c>
       <c r="E104" t="str">
         <v>200 OK</v>
@@ -3021,7 +3021,7 @@
         <v>GET</v>
       </c>
       <c r="D105">
-        <v>21.02</v>
+        <v>0</v>
       </c>
       <c r="E105" t="str">
         <v>200 OK</v>
@@ -3044,7 +3044,7 @@
         <v>GET</v>
       </c>
       <c r="D106">
-        <v>20.2</v>
+        <v>0</v>
       </c>
       <c r="E106" t="str">
         <v>200 OK</v>
@@ -3067,7 +3067,7 @@
         <v>GET</v>
       </c>
       <c r="D107">
-        <v>20.02</v>
+        <v>0</v>
       </c>
       <c r="E107" t="str">
         <v>200 OK</v>
@@ -3090,7 +3090,7 @@
         <v>GET</v>
       </c>
       <c r="D108">
-        <v>23.67</v>
+        <v>0</v>
       </c>
       <c r="E108" t="str">
         <v>200 OK</v>
@@ -3113,7 +3113,7 @@
         <v>GET</v>
       </c>
       <c r="D109">
-        <v>20.44</v>
+        <v>0</v>
       </c>
       <c r="E109" t="str">
         <v>200 OK</v>
@@ -3136,7 +3136,7 @@
         <v>GET</v>
       </c>
       <c r="D110">
-        <v>25.92</v>
+        <v>0</v>
       </c>
       <c r="E110" t="str">
         <v>200 OK</v>
@@ -3159,7 +3159,7 @@
         <v>GET</v>
       </c>
       <c r="D111">
-        <v>23.72</v>
+        <v>0</v>
       </c>
       <c r="E111" t="str">
         <v>200 OK</v>
@@ -3182,7 +3182,7 @@
         <v>GET</v>
       </c>
       <c r="D112">
-        <v>26.11</v>
+        <v>0</v>
       </c>
       <c r="E112" t="str">
         <v>200 OK</v>
@@ -3205,7 +3205,7 @@
         <v>GET</v>
       </c>
       <c r="D113">
-        <v>17.67</v>
+        <v>0</v>
       </c>
       <c r="E113" t="str">
         <v>200 OK</v>
@@ -3228,7 +3228,7 @@
         <v>GET</v>
       </c>
       <c r="D114">
-        <v>21.01</v>
+        <v>0</v>
       </c>
       <c r="E114" t="str">
         <v>200 OK</v>
@@ -3251,7 +3251,7 @@
         <v>GET</v>
       </c>
       <c r="D115">
-        <v>23.97</v>
+        <v>0</v>
       </c>
       <c r="E115" t="str">
         <v>200 OK</v>
@@ -3274,7 +3274,7 @@
         <v>GET</v>
       </c>
       <c r="D116">
-        <v>25.59</v>
+        <v>0</v>
       </c>
       <c r="E116" t="str">
         <v>200 OK</v>
@@ -3297,7 +3297,7 @@
         <v>GET</v>
       </c>
       <c r="D117">
-        <v>25.24</v>
+        <v>0</v>
       </c>
       <c r="E117" t="str">
         <v>200 OK</v>
@@ -3320,7 +3320,7 @@
         <v>GET</v>
       </c>
       <c r="D118">
-        <v>19.68</v>
+        <v>0</v>
       </c>
       <c r="E118" t="str">
         <v>200 OK</v>
@@ -3343,7 +3343,7 @@
         <v>GET</v>
       </c>
       <c r="D119">
-        <v>19.43</v>
+        <v>0</v>
       </c>
       <c r="E119" t="str">
         <v>200 OK</v>
@@ -3366,7 +3366,7 @@
         <v>GET</v>
       </c>
       <c r="D120">
-        <v>20.94</v>
+        <v>0</v>
       </c>
       <c r="E120" t="str">
         <v>200 OK</v>
@@ -3389,7 +3389,7 @@
         <v>GET</v>
       </c>
       <c r="D121">
-        <v>24.71</v>
+        <v>0</v>
       </c>
       <c r="E121" t="str">
         <v>200 OK</v>
@@ -3412,7 +3412,7 @@
         <v>GET</v>
       </c>
       <c r="D122">
-        <v>19.33</v>
+        <v>0</v>
       </c>
       <c r="E122" t="str">
         <v>200 OK</v>
@@ -3435,7 +3435,7 @@
         <v>GET</v>
       </c>
       <c r="D123">
-        <v>20.91</v>
+        <v>0</v>
       </c>
       <c r="E123" t="str">
         <v>200 OK</v>
@@ -3458,7 +3458,7 @@
         <v>GET</v>
       </c>
       <c r="D124">
-        <v>25.27</v>
+        <v>0</v>
       </c>
       <c r="E124" t="str">
         <v>200 OK</v>
@@ -3481,7 +3481,7 @@
         <v>GET</v>
       </c>
       <c r="D125">
-        <v>25.7</v>
+        <v>0</v>
       </c>
       <c r="E125" t="str">
         <v>200 OK</v>
@@ -3504,7 +3504,7 @@
         <v>GET</v>
       </c>
       <c r="D126">
-        <v>22.02</v>
+        <v>0</v>
       </c>
       <c r="E126" t="str">
         <v>200 OK</v>
@@ -3527,7 +3527,7 @@
         <v>GET</v>
       </c>
       <c r="D127">
-        <v>21.1</v>
+        <v>0</v>
       </c>
       <c r="E127" t="str">
         <v>200 OK</v>
@@ -3550,7 +3550,7 @@
         <v>GET</v>
       </c>
       <c r="D128">
-        <v>23.96</v>
+        <v>0</v>
       </c>
       <c r="E128" t="str">
         <v>200 OK</v>
@@ -3573,7 +3573,7 @@
         <v>GET</v>
       </c>
       <c r="D129">
-        <v>19.7</v>
+        <v>0</v>
       </c>
       <c r="E129" t="str">
         <v>200 OK</v>
@@ -3596,7 +3596,7 @@
         <v>GET</v>
       </c>
       <c r="D130">
-        <v>23.77</v>
+        <v>0</v>
       </c>
       <c r="E130" t="str">
         <v>200 OK</v>
@@ -3619,7 +3619,7 @@
         <v>GET</v>
       </c>
       <c r="D131">
-        <v>19.95</v>
+        <v>0</v>
       </c>
       <c r="E131" t="str">
         <v>200 OK</v>
@@ -3642,7 +3642,7 @@
         <v>GET</v>
       </c>
       <c r="D132">
-        <v>23.23</v>
+        <v>0</v>
       </c>
       <c r="E132" t="str">
         <v>200 OK</v>
@@ -3665,7 +3665,7 @@
         <v>GET</v>
       </c>
       <c r="D133">
-        <v>25.57</v>
+        <v>0</v>
       </c>
       <c r="E133" t="str">
         <v>200 OK</v>
@@ -3688,7 +3688,7 @@
         <v>GET</v>
       </c>
       <c r="D134">
-        <v>18.47</v>
+        <v>0</v>
       </c>
       <c r="E134" t="str">
         <v>200 OK</v>
@@ -3711,7 +3711,7 @@
         <v>GET</v>
       </c>
       <c r="D135">
-        <v>23.7</v>
+        <v>0</v>
       </c>
       <c r="E135" t="str">
         <v>200 OK</v>
@@ -3734,7 +3734,7 @@
         <v>GET</v>
       </c>
       <c r="D136">
-        <v>17.44</v>
+        <v>0</v>
       </c>
       <c r="E136" t="str">
         <v>200 OK</v>
@@ -3757,7 +3757,7 @@
         <v>GET</v>
       </c>
       <c r="D137">
-        <v>18.99</v>
+        <v>0</v>
       </c>
       <c r="E137" t="str">
         <v>200 OK</v>
@@ -3780,7 +3780,7 @@
         <v>GET</v>
       </c>
       <c r="D138">
-        <v>22.97</v>
+        <v>0</v>
       </c>
       <c r="E138" t="str">
         <v>200 OK</v>
@@ -3803,7 +3803,7 @@
         <v>GET</v>
       </c>
       <c r="D139">
-        <v>23.05</v>
+        <v>0</v>
       </c>
       <c r="E139" t="str">
         <v>200 OK</v>
@@ -3826,7 +3826,7 @@
         <v>GET</v>
       </c>
       <c r="D140">
-        <v>17.69</v>
+        <v>0</v>
       </c>
       <c r="E140" t="str">
         <v>200 OK</v>
@@ -3849,7 +3849,7 @@
         <v>GET</v>
       </c>
       <c r="D141">
-        <v>20.33</v>
+        <v>0</v>
       </c>
       <c r="E141" t="str">
         <v>200 OK</v>
@@ -3872,7 +3872,7 @@
         <v>GET</v>
       </c>
       <c r="D142">
-        <v>20.13</v>
+        <v>0</v>
       </c>
       <c r="E142" t="str">
         <v>200 OK</v>
@@ -3895,7 +3895,7 @@
         <v>GET</v>
       </c>
       <c r="D143">
-        <v>18.73</v>
+        <v>0</v>
       </c>
       <c r="E143" t="str">
         <v>200 OK</v>
@@ -3918,7 +3918,7 @@
         <v>GET</v>
       </c>
       <c r="D144">
-        <v>19.73</v>
+        <v>0</v>
       </c>
       <c r="E144" t="str">
         <v>200 OK</v>
@@ -3941,7 +3941,7 @@
         <v>GET</v>
       </c>
       <c r="D145">
-        <v>19.99</v>
+        <v>0</v>
       </c>
       <c r="E145" t="str">
         <v>200 OK</v>
@@ -3964,7 +3964,7 @@
         <v>GET</v>
       </c>
       <c r="D146">
-        <v>23.95</v>
+        <v>0</v>
       </c>
       <c r="E146" t="str">
         <v>200 OK</v>
@@ -3987,7 +3987,7 @@
         <v>GET</v>
       </c>
       <c r="D147">
-        <v>21.29</v>
+        <v>0</v>
       </c>
       <c r="E147" t="str">
         <v>200 OK</v>
@@ -4010,7 +4010,7 @@
         <v>GET</v>
       </c>
       <c r="D148">
-        <v>21.52</v>
+        <v>0</v>
       </c>
       <c r="E148" t="str">
         <v>200 OK</v>
@@ -4033,7 +4033,7 @@
         <v>GET</v>
       </c>
       <c r="D149">
-        <v>25.23</v>
+        <v>0</v>
       </c>
       <c r="E149" t="str">
         <v>200 OK</v>
@@ -4056,7 +4056,7 @@
         <v>GET</v>
       </c>
       <c r="D150">
-        <v>21.25</v>
+        <v>0</v>
       </c>
       <c r="E150" t="str">
         <v>200 OK</v>
@@ -4079,7 +4079,7 @@
         <v>GET</v>
       </c>
       <c r="D151">
-        <v>24.23</v>
+        <v>0</v>
       </c>
       <c r="E151" t="str">
         <v>200 OK</v>
@@ -4102,7 +4102,7 @@
         <v>GET</v>
       </c>
       <c r="D152">
-        <v>19.69</v>
+        <v>0</v>
       </c>
       <c r="E152" t="str">
         <v>200 OK</v>
@@ -4125,7 +4125,7 @@
         <v>GET</v>
       </c>
       <c r="D153">
-        <v>24.43</v>
+        <v>0</v>
       </c>
       <c r="E153" t="str">
         <v>200 OK</v>
@@ -4148,7 +4148,7 @@
         <v>GET</v>
       </c>
       <c r="D154">
-        <v>21.38</v>
+        <v>0</v>
       </c>
       <c r="E154" t="str">
         <v>200 OK</v>
@@ -4171,7 +4171,7 @@
         <v>GET</v>
       </c>
       <c r="D155">
-        <v>22.93</v>
+        <v>0</v>
       </c>
       <c r="E155" t="str">
         <v>200 OK</v>
@@ -4194,7 +4194,7 @@
         <v>GET</v>
       </c>
       <c r="D156">
-        <v>23.04</v>
+        <v>0</v>
       </c>
       <c r="E156" t="str">
         <v>200 OK</v>
@@ -4217,7 +4217,7 @@
         <v>GET</v>
       </c>
       <c r="D157">
-        <v>25.79</v>
+        <v>0</v>
       </c>
       <c r="E157" t="str">
         <v>200 OK</v>
@@ -4240,7 +4240,7 @@
         <v>GET</v>
       </c>
       <c r="D158">
-        <v>25.11</v>
+        <v>0</v>
       </c>
       <c r="E158" t="str">
         <v>200 OK</v>
@@ -4263,7 +4263,7 @@
         <v>GET</v>
       </c>
       <c r="D159">
-        <v>21.05</v>
+        <v>0</v>
       </c>
       <c r="E159" t="str">
         <v>200 OK</v>
@@ -4286,7 +4286,7 @@
         <v>GET</v>
       </c>
       <c r="D160">
-        <v>22.63</v>
+        <v>0</v>
       </c>
       <c r="E160" t="str">
         <v>200 OK</v>
@@ -4309,7 +4309,7 @@
         <v>GET</v>
       </c>
       <c r="D161">
-        <v>21.49</v>
+        <v>0</v>
       </c>
       <c r="E161" t="str">
         <v>200 OK</v>
@@ -4332,7 +4332,7 @@
         <v>GET</v>
       </c>
       <c r="D162">
-        <v>19.18</v>
+        <v>0</v>
       </c>
       <c r="E162" t="str">
         <v>200 OK</v>
@@ -4355,7 +4355,7 @@
         <v>GET</v>
       </c>
       <c r="D163">
-        <v>22.86</v>
+        <v>0</v>
       </c>
       <c r="E163" t="str">
         <v>200 OK</v>
@@ -4378,7 +4378,7 @@
         <v>GET</v>
       </c>
       <c r="D164">
-        <v>21.82</v>
+        <v>0</v>
       </c>
       <c r="E164" t="str">
         <v>200 OK</v>
@@ -4401,7 +4401,7 @@
         <v>GET</v>
       </c>
       <c r="D165">
-        <v>21.6</v>
+        <v>0</v>
       </c>
       <c r="E165" t="str">
         <v>200 OK</v>
@@ -4424,7 +4424,7 @@
         <v>GET</v>
       </c>
       <c r="D166">
-        <v>21.44</v>
+        <v>0</v>
       </c>
       <c r="E166" t="str">
         <v>200 OK</v>
@@ -4447,7 +4447,7 @@
         <v>GET</v>
       </c>
       <c r="D167">
-        <v>19.32</v>
+        <v>0</v>
       </c>
       <c r="E167" t="str">
         <v>200 OK</v>
@@ -4470,7 +4470,7 @@
         <v>GET</v>
       </c>
       <c r="D168">
-        <v>23.09</v>
+        <v>0</v>
       </c>
       <c r="E168" t="str">
         <v>200 OK</v>
@@ -4493,7 +4493,7 @@
         <v>GET</v>
       </c>
       <c r="D169">
-        <v>22.14</v>
+        <v>0</v>
       </c>
       <c r="E169" t="str">
         <v>200 OK</v>
@@ -4516,7 +4516,7 @@
         <v>GET</v>
       </c>
       <c r="D170">
-        <v>22.61</v>
+        <v>0</v>
       </c>
       <c r="E170" t="str">
         <v>200 OK</v>
@@ -4539,7 +4539,7 @@
         <v>GET</v>
       </c>
       <c r="D171">
-        <v>18.96</v>
+        <v>0</v>
       </c>
       <c r="E171" t="str">
         <v>200 OK</v>
@@ -4562,7 +4562,7 @@
         <v>GET</v>
       </c>
       <c r="D172">
-        <v>21.43</v>
+        <v>0</v>
       </c>
       <c r="E172" t="str">
         <v>200 OK</v>
@@ -4585,7 +4585,7 @@
         <v>GET</v>
       </c>
       <c r="D173">
-        <v>22.19</v>
+        <v>0</v>
       </c>
       <c r="E173" t="str">
         <v>200 OK</v>
@@ -4608,7 +4608,7 @@
         <v>GET</v>
       </c>
       <c r="D174">
-        <v>21.91</v>
+        <v>0</v>
       </c>
       <c r="E174" t="str">
         <v>200 OK</v>
@@ -4631,7 +4631,7 @@
         <v>GET</v>
       </c>
       <c r="D175">
-        <v>19.56</v>
+        <v>0</v>
       </c>
       <c r="E175" t="str">
         <v>200 OK</v>
@@ -4654,7 +4654,7 @@
         <v>GET</v>
       </c>
       <c r="D176">
-        <v>24.72</v>
+        <v>0</v>
       </c>
       <c r="E176" t="str">
         <v>200 OK</v>
@@ -4677,7 +4677,7 @@
         <v>GET</v>
       </c>
       <c r="D177">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="E177" t="str">
         <v>200 OK</v>
@@ -4700,7 +4700,7 @@
         <v>GET</v>
       </c>
       <c r="D178">
-        <v>19.25</v>
+        <v>0</v>
       </c>
       <c r="E178" t="str">
         <v>200 OK</v>
@@ -4723,7 +4723,7 @@
         <v>GET</v>
       </c>
       <c r="D179">
-        <v>18.9</v>
+        <v>0</v>
       </c>
       <c r="E179" t="str">
         <v>200 OK</v>
@@ -4746,7 +4746,7 @@
         <v>GET</v>
       </c>
       <c r="D180">
-        <v>22.49</v>
+        <v>0</v>
       </c>
       <c r="E180" t="str">
         <v>200 OK</v>
@@ -4769,7 +4769,7 @@
         <v>GET</v>
       </c>
       <c r="D181">
-        <v>21.76</v>
+        <v>0</v>
       </c>
       <c r="E181" t="str">
         <v>200 OK</v>
@@ -4792,7 +4792,7 @@
         <v>GET</v>
       </c>
       <c r="D182">
-        <v>18.01</v>
+        <v>0</v>
       </c>
       <c r="E182" t="str">
         <v>200 OK</v>
@@ -4815,7 +4815,7 @@
         <v>GET</v>
       </c>
       <c r="D183">
-        <v>22.9</v>
+        <v>0</v>
       </c>
       <c r="E183" t="str">
         <v>200 OK</v>
@@ -4838,7 +4838,7 @@
         <v>GET</v>
       </c>
       <c r="D184">
-        <v>22.09</v>
+        <v>0</v>
       </c>
       <c r="E184" t="str">
         <v>200 OK</v>
@@ -4861,7 +4861,7 @@
         <v>GET</v>
       </c>
       <c r="D185">
-        <v>22.98</v>
+        <v>0</v>
       </c>
       <c r="E185" t="str">
         <v>200 OK</v>
@@ -4884,7 +4884,7 @@
         <v>GET</v>
       </c>
       <c r="D186">
-        <v>22.42</v>
+        <v>0</v>
       </c>
       <c r="E186" t="str">
         <v>200 OK</v>
@@ -4907,7 +4907,7 @@
         <v>GET</v>
       </c>
       <c r="D187">
-        <v>24.74</v>
+        <v>0</v>
       </c>
       <c r="E187" t="str">
         <v>200 OK</v>
@@ -4930,7 +4930,7 @@
         <v>GET</v>
       </c>
       <c r="D188">
-        <v>22.71</v>
+        <v>0</v>
       </c>
       <c r="E188" t="str">
         <v>200 OK</v>
@@ -4953,7 +4953,7 @@
         <v>GET</v>
       </c>
       <c r="D189">
-        <v>19.83</v>
+        <v>0</v>
       </c>
       <c r="E189" t="str">
         <v>200 OK</v>
@@ -4976,7 +4976,7 @@
         <v>GET</v>
       </c>
       <c r="D190">
-        <v>25.56</v>
+        <v>0</v>
       </c>
       <c r="E190" t="str">
         <v>200 OK</v>
@@ -4999,7 +4999,7 @@
         <v>GET</v>
       </c>
       <c r="D191">
-        <v>23.95</v>
+        <v>0</v>
       </c>
       <c r="E191" t="str">
         <v>200 OK</v>
@@ -5022,7 +5022,7 @@
         <v>GET</v>
       </c>
       <c r="D192">
-        <v>20.98</v>
+        <v>0</v>
       </c>
       <c r="E192" t="str">
         <v>200 OK</v>
@@ -5045,7 +5045,7 @@
         <v>GET</v>
       </c>
       <c r="D193">
-        <v>25.19</v>
+        <v>0</v>
       </c>
       <c r="E193" t="str">
         <v>200 OK</v>
@@ -5068,7 +5068,7 @@
         <v>GET</v>
       </c>
       <c r="D194">
-        <v>22.28</v>
+        <v>0</v>
       </c>
       <c r="E194" t="str">
         <v>200 OK</v>
@@ -5091,7 +5091,7 @@
         <v>GET</v>
       </c>
       <c r="D195">
-        <v>17.59</v>
+        <v>0</v>
       </c>
       <c r="E195" t="str">
         <v>200 OK</v>
@@ -5114,7 +5114,7 @@
         <v>GET</v>
       </c>
       <c r="D196">
-        <v>20.1</v>
+        <v>0</v>
       </c>
       <c r="E196" t="str">
         <v>200 OK</v>
@@ -5137,7 +5137,7 @@
         <v>GET</v>
       </c>
       <c r="D197">
-        <v>22.23</v>
+        <v>0</v>
       </c>
       <c r="E197" t="str">
         <v>200 OK</v>
@@ -5160,7 +5160,7 @@
         <v>GET</v>
       </c>
       <c r="D198">
-        <v>24.03</v>
+        <v>0</v>
       </c>
       <c r="E198" t="str">
         <v>200 OK</v>
@@ -5183,7 +5183,7 @@
         <v>GET</v>
       </c>
       <c r="D199">
-        <v>23.16</v>
+        <v>0</v>
       </c>
       <c r="E199" t="str">
         <v>200 OK</v>
@@ -5206,7 +5206,7 @@
         <v>GET</v>
       </c>
       <c r="D200">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="E200" t="str">
         <v>200 OK</v>
@@ -5229,7 +5229,7 @@
         <v>GET</v>
       </c>
       <c r="D201">
-        <v>23.85</v>
+        <v>0</v>
       </c>
       <c r="E201" t="str">
         <v>200 OK</v>
@@ -5252,7 +5252,7 @@
         <v>GET</v>
       </c>
       <c r="D202">
-        <v>21.61</v>
+        <v>0</v>
       </c>
       <c r="E202" t="str">
         <v>200 OK</v>
@@ -5275,7 +5275,7 @@
         <v>GET</v>
       </c>
       <c r="D203">
-        <v>19.45</v>
+        <v>0</v>
       </c>
       <c r="E203" t="str">
         <v>200 OK</v>
@@ -5298,7 +5298,7 @@
         <v>GET</v>
       </c>
       <c r="D204">
-        <v>19.79</v>
+        <v>0</v>
       </c>
       <c r="E204" t="str">
         <v>200 OK</v>
@@ -5321,7 +5321,7 @@
         <v>GET</v>
       </c>
       <c r="D205">
-        <v>21.78</v>
+        <v>0</v>
       </c>
       <c r="E205" t="str">
         <v>200 OK</v>
@@ -5344,7 +5344,7 @@
         <v>GET</v>
       </c>
       <c r="D206">
-        <v>18.72</v>
+        <v>0</v>
       </c>
       <c r="E206" t="str">
         <v>200 OK</v>
@@ -5367,7 +5367,7 @@
         <v>GET</v>
       </c>
       <c r="D207">
-        <v>21.34</v>
+        <v>0</v>
       </c>
       <c r="E207" t="str">
         <v>200 OK</v>
@@ -5390,7 +5390,7 @@
         <v>GET</v>
       </c>
       <c r="D208">
-        <v>19.8</v>
+        <v>0</v>
       </c>
       <c r="E208" t="str">
         <v>200 OK</v>
@@ -5413,7 +5413,7 @@
         <v>GET</v>
       </c>
       <c r="D209">
-        <v>25.93</v>
+        <v>0</v>
       </c>
       <c r="E209" t="str">
         <v>200 OK</v>
@@ -5436,7 +5436,7 @@
         <v>GET</v>
       </c>
       <c r="D210">
-        <v>19.7</v>
+        <v>0</v>
       </c>
       <c r="E210" t="str">
         <v>200 OK</v>
@@ -5459,7 +5459,7 @@
         <v>GET</v>
       </c>
       <c r="D211">
-        <v>21.12</v>
+        <v>0</v>
       </c>
       <c r="E211" t="str">
         <v>200 OK</v>
@@ -5482,7 +5482,7 @@
         <v>GET</v>
       </c>
       <c r="D212">
-        <v>23.84</v>
+        <v>0</v>
       </c>
       <c r="E212" t="str">
         <v>200 OK</v>
@@ -5505,7 +5505,7 @@
         <v>GET</v>
       </c>
       <c r="D213">
-        <v>21.9</v>
+        <v>0</v>
       </c>
       <c r="E213" t="str">
         <v>200 OK</v>
@@ -5528,7 +5528,7 @@
         <v>GET</v>
       </c>
       <c r="D214">
-        <v>18.37</v>
+        <v>0</v>
       </c>
       <c r="E214" t="str">
         <v>200 OK</v>
@@ -5551,7 +5551,7 @@
         <v>GET</v>
       </c>
       <c r="D215">
-        <v>19.67</v>
+        <v>0</v>
       </c>
       <c r="E215" t="str">
         <v>200 OK</v>
@@ -5574,7 +5574,7 @@
         <v>GET</v>
       </c>
       <c r="D216">
-        <v>22.86</v>
+        <v>0</v>
       </c>
       <c r="E216" t="str">
         <v>200 OK</v>
@@ -5597,7 +5597,7 @@
         <v>GET</v>
       </c>
       <c r="D217">
-        <v>18.48</v>
+        <v>0</v>
       </c>
       <c r="E217" t="str">
         <v>200 OK</v>
@@ -5620,7 +5620,7 @@
         <v>GET</v>
       </c>
       <c r="D218">
-        <v>20.51</v>
+        <v>0</v>
       </c>
       <c r="E218" t="str">
         <v>200 OK</v>
@@ -5643,7 +5643,7 @@
         <v>GET</v>
       </c>
       <c r="D219">
-        <v>17.72</v>
+        <v>0</v>
       </c>
       <c r="E219" t="str">
         <v>200 OK</v>
@@ -5666,7 +5666,7 @@
         <v>GET</v>
       </c>
       <c r="D220">
-        <v>21.33</v>
+        <v>0</v>
       </c>
       <c r="E220" t="str">
         <v>200 OK</v>
@@ -5689,7 +5689,7 @@
         <v>GET</v>
       </c>
       <c r="D221">
-        <v>23.16</v>
+        <v>0</v>
       </c>
       <c r="E221" t="str">
         <v>200 OK</v>
@@ -5712,7 +5712,7 @@
         <v>GET</v>
       </c>
       <c r="D222">
-        <v>19.85</v>
+        <v>0</v>
       </c>
       <c r="E222" t="str">
         <v>200 OK</v>
@@ -5735,7 +5735,7 @@
         <v>GET</v>
       </c>
       <c r="D223">
-        <v>17.87</v>
+        <v>0</v>
       </c>
       <c r="E223" t="str">
         <v>200 OK</v>
@@ -5758,7 +5758,7 @@
         <v>GET</v>
       </c>
       <c r="D224">
-        <v>24.62</v>
+        <v>0</v>
       </c>
       <c r="E224" t="str">
         <v>200 OK</v>
@@ -5781,7 +5781,7 @@
         <v>GET</v>
       </c>
       <c r="D225">
-        <v>22.84</v>
+        <v>0</v>
       </c>
       <c r="E225" t="str">
         <v>200 OK</v>
@@ -5804,7 +5804,7 @@
         <v>GET</v>
       </c>
       <c r="D226">
-        <v>20.92</v>
+        <v>0</v>
       </c>
       <c r="E226" t="str">
         <v>200 OK</v>
@@ -5827,7 +5827,7 @@
         <v>GET</v>
       </c>
       <c r="D227">
-        <v>23.07</v>
+        <v>0</v>
       </c>
       <c r="E227" t="str">
         <v>200 OK</v>
@@ -5850,7 +5850,7 @@
         <v>GET</v>
       </c>
       <c r="D228">
-        <v>20.09</v>
+        <v>0</v>
       </c>
       <c r="E228" t="str">
         <v>200 OK</v>
@@ -5873,7 +5873,7 @@
         <v>GET</v>
       </c>
       <c r="D229">
-        <v>17.52</v>
+        <v>0</v>
       </c>
       <c r="E229" t="str">
         <v>200 OK</v>
@@ -5896,7 +5896,7 @@
         <v>GET</v>
       </c>
       <c r="D230">
-        <v>23.96</v>
+        <v>0</v>
       </c>
       <c r="E230" t="str">
         <v>200 OK</v>
@@ -5919,7 +5919,7 @@
         <v>GET</v>
       </c>
       <c r="D231">
-        <v>17.73</v>
+        <v>0</v>
       </c>
       <c r="E231" t="str">
         <v>200 OK</v>
@@ -5942,7 +5942,7 @@
         <v>GET</v>
       </c>
       <c r="D232">
-        <v>21.9</v>
+        <v>0</v>
       </c>
       <c r="E232" t="str">
         <v>200 OK</v>
@@ -5965,7 +5965,7 @@
         <v>GET</v>
       </c>
       <c r="D233">
-        <v>21.54</v>
+        <v>0</v>
       </c>
       <c r="E233" t="str">
         <v>200 OK</v>
@@ -5988,7 +5988,7 @@
         <v>GET</v>
       </c>
       <c r="D234">
-        <v>20.08</v>
+        <v>0</v>
       </c>
       <c r="E234" t="str">
         <v>200 OK</v>
@@ -6011,7 +6011,7 @@
         <v>GET</v>
       </c>
       <c r="D235">
-        <v>22.97</v>
+        <v>0</v>
       </c>
       <c r="E235" t="str">
         <v>200 OK</v>
@@ -6034,7 +6034,7 @@
         <v>GET</v>
       </c>
       <c r="D236">
-        <v>22.62</v>
+        <v>0</v>
       </c>
       <c r="E236" t="str">
         <v>200 OK</v>
@@ -6057,7 +6057,7 @@
         <v>GET</v>
       </c>
       <c r="D237">
-        <v>19.82</v>
+        <v>0</v>
       </c>
       <c r="E237" t="str">
         <v>200 OK</v>
@@ -6080,7 +6080,7 @@
         <v>GET</v>
       </c>
       <c r="D238">
-        <v>25.25</v>
+        <v>0</v>
       </c>
       <c r="E238" t="str">
         <v>200 OK</v>
@@ -6103,7 +6103,7 @@
         <v>GET</v>
       </c>
       <c r="D239">
-        <v>22.11</v>
+        <v>0</v>
       </c>
       <c r="E239" t="str">
         <v>200 OK</v>
@@ -6126,7 +6126,7 @@
         <v>GET</v>
       </c>
       <c r="D240">
-        <v>21.49</v>
+        <v>0</v>
       </c>
       <c r="E240" t="str">
         <v>200 OK</v>
@@ -6149,7 +6149,7 @@
         <v>GET</v>
       </c>
       <c r="D241">
-        <v>23.88</v>
+        <v>0</v>
       </c>
       <c r="E241" t="str">
         <v>200 OK</v>
@@ -6172,7 +6172,7 @@
         <v>GET</v>
       </c>
       <c r="D242">
-        <v>21.67</v>
+        <v>0</v>
       </c>
       <c r="E242" t="str">
         <v>200 OK</v>
@@ -6195,7 +6195,7 @@
         <v>GET</v>
       </c>
       <c r="D243">
-        <v>21.18</v>
+        <v>0</v>
       </c>
       <c r="E243" t="str">
         <v>200 OK</v>
@@ -6218,7 +6218,7 @@
         <v>GET</v>
       </c>
       <c r="D244">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E244" t="str">
         <v>200 OK</v>
@@ -6241,7 +6241,7 @@
         <v>GET</v>
       </c>
       <c r="D245">
-        <v>18.15</v>
+        <v>0</v>
       </c>
       <c r="E245" t="str">
         <v>200 OK</v>
@@ -6264,7 +6264,7 @@
         <v>GET</v>
       </c>
       <c r="D246">
-        <v>26.05</v>
+        <v>0</v>
       </c>
       <c r="E246" t="str">
         <v>200 OK</v>
@@ -6287,7 +6287,7 @@
         <v>GET</v>
       </c>
       <c r="D247">
-        <v>21.54</v>
+        <v>0</v>
       </c>
       <c r="E247" t="str">
         <v>200 OK</v>
@@ -6310,7 +6310,7 @@
         <v>GET</v>
       </c>
       <c r="D248">
-        <v>19.4</v>
+        <v>0</v>
       </c>
       <c r="E248" t="str">
         <v>200 OK</v>
@@ -6333,7 +6333,7 @@
         <v>GET</v>
       </c>
       <c r="D249">
-        <v>22.25</v>
+        <v>0</v>
       </c>
       <c r="E249" t="str">
         <v>200 OK</v>
@@ -6356,7 +6356,7 @@
         <v>GET</v>
       </c>
       <c r="D250">
-        <v>21.32</v>
+        <v>0</v>
       </c>
       <c r="E250" t="str">
         <v>200 OK</v>
@@ -6379,7 +6379,7 @@
         <v>GET</v>
       </c>
       <c r="D251">
-        <v>18.21</v>
+        <v>0</v>
       </c>
       <c r="E251" t="str">
         <v>200 OK</v>
@@ -6402,7 +6402,7 @@
         <v>GET</v>
       </c>
       <c r="D252">
-        <v>20.79</v>
+        <v>0</v>
       </c>
       <c r="E252" t="str">
         <v>200 OK</v>
@@ -6425,7 +6425,7 @@
         <v>GET</v>
       </c>
       <c r="D253">
-        <v>18.49</v>
+        <v>0</v>
       </c>
       <c r="E253" t="str">
         <v>200 OK</v>
@@ -6448,7 +6448,7 @@
         <v>GET</v>
       </c>
       <c r="D254">
-        <v>18.53</v>
+        <v>0</v>
       </c>
       <c r="E254" t="str">
         <v>200 OK</v>
@@ -6471,7 +6471,7 @@
         <v>GET</v>
       </c>
       <c r="D255">
-        <v>19.67</v>
+        <v>0</v>
       </c>
       <c r="E255" t="str">
         <v>200 OK</v>
@@ -6494,7 +6494,7 @@
         <v>GET</v>
       </c>
       <c r="D256">
-        <v>25.75</v>
+        <v>0</v>
       </c>
       <c r="E256" t="str">
         <v>200 OK</v>
@@ -6517,7 +6517,7 @@
         <v>GET</v>
       </c>
       <c r="D257">
-        <v>24.1</v>
+        <v>0</v>
       </c>
       <c r="E257" t="str">
         <v>200 OK</v>
@@ -6540,7 +6540,7 @@
         <v>GET</v>
       </c>
       <c r="D258">
-        <v>17.98</v>
+        <v>0</v>
       </c>
       <c r="E258" t="str">
         <v>200 OK</v>
@@ -6563,7 +6563,7 @@
         <v>GET</v>
       </c>
       <c r="D259">
-        <v>23.54</v>
+        <v>0</v>
       </c>
       <c r="E259" t="str">
         <v>200 OK</v>
@@ -6586,7 +6586,7 @@
         <v>GET</v>
       </c>
       <c r="D260">
-        <v>25.7</v>
+        <v>0</v>
       </c>
       <c r="E260" t="str">
         <v>200 OK</v>
@@ -6609,7 +6609,7 @@
         <v>GET</v>
       </c>
       <c r="D261">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="E261" t="str">
         <v>200 OK</v>
@@ -6632,7 +6632,7 @@
         <v>GET</v>
       </c>
       <c r="D262">
-        <v>21.96</v>
+        <v>0</v>
       </c>
       <c r="E262" t="str">
         <v>200 OK</v>
@@ -6655,7 +6655,7 @@
         <v>GET</v>
       </c>
       <c r="D263">
-        <v>21.54</v>
+        <v>0</v>
       </c>
       <c r="E263" t="str">
         <v>200 OK</v>
@@ -6678,7 +6678,7 @@
         <v>GET</v>
       </c>
       <c r="D264">
-        <v>23.36</v>
+        <v>0</v>
       </c>
       <c r="E264" t="str">
         <v>200 OK</v>
@@ -6701,7 +6701,7 @@
         <v>GET</v>
       </c>
       <c r="D265">
-        <v>23.62</v>
+        <v>0</v>
       </c>
       <c r="E265" t="str">
         <v>200 OK</v>
@@ -6724,7 +6724,7 @@
         <v>GET</v>
       </c>
       <c r="D266">
-        <v>18.4</v>
+        <v>0</v>
       </c>
       <c r="E266" t="str">
         <v>200 OK</v>
@@ -6747,7 +6747,7 @@
         <v>GET</v>
       </c>
       <c r="D267">
-        <v>19.41</v>
+        <v>0</v>
       </c>
       <c r="E267" t="str">
         <v>200 OK</v>
@@ -6770,7 +6770,7 @@
         <v>GET</v>
       </c>
       <c r="D268">
-        <v>24.19</v>
+        <v>0</v>
       </c>
       <c r="E268" t="str">
         <v>200 OK</v>
@@ -6793,7 +6793,7 @@
         <v>GET</v>
       </c>
       <c r="D269">
-        <v>18.74</v>
+        <v>0</v>
       </c>
       <c r="E269" t="str">
         <v>200 OK</v>
@@ -6816,7 +6816,7 @@
         <v>GET</v>
       </c>
       <c r="D270">
-        <v>22.74</v>
+        <v>0</v>
       </c>
       <c r="E270" t="str">
         <v>200 OK</v>
@@ -6839,7 +6839,7 @@
         <v>GET</v>
       </c>
       <c r="D271">
-        <v>19.91</v>
+        <v>0</v>
       </c>
       <c r="E271" t="str">
         <v>200 OK</v>
@@ -6862,7 +6862,7 @@
         <v>GET</v>
       </c>
       <c r="D272">
-        <v>22.24</v>
+        <v>0</v>
       </c>
       <c r="E272" t="str">
         <v>200 OK</v>
@@ -6885,7 +6885,7 @@
         <v>GET</v>
       </c>
       <c r="D273">
-        <v>25.11</v>
+        <v>0</v>
       </c>
       <c r="E273" t="str">
         <v>200 OK</v>
@@ -6908,7 +6908,7 @@
         <v>GET</v>
       </c>
       <c r="D274">
-        <v>22.39</v>
+        <v>0</v>
       </c>
       <c r="E274" t="str">
         <v>200 OK</v>
@@ -6931,7 +6931,7 @@
         <v>GET</v>
       </c>
       <c r="D275">
-        <v>18.77</v>
+        <v>0</v>
       </c>
       <c r="E275" t="str">
         <v>200 OK</v>
@@ -6954,7 +6954,7 @@
         <v>GET</v>
       </c>
       <c r="D276">
-        <v>22.35</v>
+        <v>0</v>
       </c>
       <c r="E276" t="str">
         <v>200 OK</v>
@@ -6977,7 +6977,7 @@
         <v>GET</v>
       </c>
       <c r="D277">
-        <v>23.95</v>
+        <v>0</v>
       </c>
       <c r="E277" t="str">
         <v>200 OK</v>
@@ -7000,7 +7000,7 @@
         <v>GET</v>
       </c>
       <c r="D278">
-        <v>23.59</v>
+        <v>0</v>
       </c>
       <c r="E278" t="str">
         <v>200 OK</v>
@@ -7023,7 +7023,7 @@
         <v>GET</v>
       </c>
       <c r="D279">
-        <v>23.94</v>
+        <v>0</v>
       </c>
       <c r="E279" t="str">
         <v>200 OK</v>
@@ -7046,7 +7046,7 @@
         <v>GET</v>
       </c>
       <c r="D280">
-        <v>18.32</v>
+        <v>0</v>
       </c>
       <c r="E280" t="str">
         <v>200 OK</v>
@@ -7069,7 +7069,7 @@
         <v>GET</v>
       </c>
       <c r="D281">
-        <v>23.4</v>
+        <v>0</v>
       </c>
       <c r="E281" t="str">
         <v>200 OK</v>
@@ -7092,7 +7092,7 @@
         <v>GET</v>
       </c>
       <c r="D282">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="E282" t="str">
         <v>200 OK</v>
@@ -7115,7 +7115,7 @@
         <v>GET</v>
       </c>
       <c r="D283">
-        <v>20.96</v>
+        <v>0</v>
       </c>
       <c r="E283" t="str">
         <v>200 OK</v>
@@ -7138,7 +7138,7 @@
         <v>GET</v>
       </c>
       <c r="D284">
-        <v>20.96</v>
+        <v>0</v>
       </c>
       <c r="E284" t="str">
         <v>200 OK</v>
@@ -7161,7 +7161,7 @@
         <v>GET</v>
       </c>
       <c r="D285">
-        <v>22.25</v>
+        <v>0</v>
       </c>
       <c r="E285" t="str">
         <v>200 OK</v>
@@ -7184,7 +7184,7 @@
         <v>GET</v>
       </c>
       <c r="D286">
-        <v>25.69</v>
+        <v>0</v>
       </c>
       <c r="E286" t="str">
         <v>200 OK</v>
@@ -7207,7 +7207,7 @@
         <v>GET</v>
       </c>
       <c r="D287">
-        <v>21.76</v>
+        <v>0</v>
       </c>
       <c r="E287" t="str">
         <v>200 OK</v>
@@ -7230,7 +7230,7 @@
         <v>GET</v>
       </c>
       <c r="D288">
-        <v>23.92</v>
+        <v>0</v>
       </c>
       <c r="E288" t="str">
         <v>200 OK</v>
@@ -7253,7 +7253,7 @@
         <v>GET</v>
       </c>
       <c r="D289">
-        <v>19.97</v>
+        <v>0</v>
       </c>
       <c r="E289" t="str">
         <v>200 OK</v>
@@ -7276,7 +7276,7 @@
         <v>GET</v>
       </c>
       <c r="D290">
-        <v>24.57</v>
+        <v>0</v>
       </c>
       <c r="E290" t="str">
         <v>200 OK</v>
@@ -7299,7 +7299,7 @@
         <v>GET</v>
       </c>
       <c r="D291">
-        <v>24.05</v>
+        <v>0</v>
       </c>
       <c r="E291" t="str">
         <v>200 OK</v>
@@ -7322,7 +7322,7 @@
         <v>GET</v>
       </c>
       <c r="D292">
-        <v>21.86</v>
+        <v>0</v>
       </c>
       <c r="E292" t="str">
         <v>200 OK</v>
@@ -7345,7 +7345,7 @@
         <v>GET</v>
       </c>
       <c r="D293">
-        <v>22.99</v>
+        <v>0</v>
       </c>
       <c r="E293" t="str">
         <v>200 OK</v>
@@ -7368,7 +7368,7 @@
         <v>GET</v>
       </c>
       <c r="D294">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="E294" t="str">
         <v>200 OK</v>
@@ -7391,7 +7391,7 @@
         <v>GET</v>
       </c>
       <c r="D295">
-        <v>17.54</v>
+        <v>0</v>
       </c>
       <c r="E295" t="str">
         <v>200 OK</v>
@@ -7414,7 +7414,7 @@
         <v>GET</v>
       </c>
       <c r="D296">
-        <v>22.82</v>
+        <v>0</v>
       </c>
       <c r="E296" t="str">
         <v>200 OK</v>
@@ -7437,7 +7437,7 @@
         <v>GET</v>
       </c>
       <c r="D297">
-        <v>19.86</v>
+        <v>0</v>
       </c>
       <c r="E297" t="str">
         <v>200 OK</v>
@@ -7460,7 +7460,7 @@
         <v>GET</v>
       </c>
       <c r="D298">
-        <v>25.96</v>
+        <v>0</v>
       </c>
       <c r="E298" t="str">
         <v>200 OK</v>
@@ -7483,7 +7483,7 @@
         <v>GET</v>
       </c>
       <c r="D299">
-        <v>23.82</v>
+        <v>0</v>
       </c>
       <c r="E299" t="str">
         <v>200 OK</v>
@@ -7506,7 +7506,7 @@
         <v>GET</v>
       </c>
       <c r="D300">
-        <v>17.93</v>
+        <v>0</v>
       </c>
       <c r="E300" t="str">
         <v>200 OK</v>
@@ -7529,7 +7529,7 @@
         <v>GET</v>
       </c>
       <c r="D301">
-        <v>21.31</v>
+        <v>0</v>
       </c>
       <c r="E301" t="str">
         <v>200 OK</v>

--- a/load-tests/load-test-report.xlsx
+++ b/load-tests/load-test-report.xlsx
@@ -444,7 +444,7 @@
         <v>Duration (seconds)</v>
       </c>
       <c r="B4">
-        <v>10.14</v>
+        <v>10.2</v>
       </c>
       <c r="C4" t="str">
         <v>Length of benchmarking</v>
@@ -607,7 +607,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G301"/>
+  <dimension ref="A1:H301"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -635,9 +635,12 @@
         <v>Status</v>
       </c>
       <c r="F1" t="str">
+        <v>HTTP Response</v>
+      </c>
+      <c r="G1" t="str">
         <v>Bytes Sent</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>Concurrent Users</v>
       </c>
     </row>
@@ -655,12 +658,15 @@
         <v>0</v>
       </c>
       <c r="E2" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F2">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F2" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G2">
+        <v>105</v>
+      </c>
+      <c r="H2">
         <v>100</v>
       </c>
     </row>
@@ -678,12 +684,15 @@
         <v>0</v>
       </c>
       <c r="E3" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F3">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F3" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G3">
+        <v>105</v>
+      </c>
+      <c r="H3">
         <v>100</v>
       </c>
     </row>
@@ -701,12 +710,15 @@
         <v>0</v>
       </c>
       <c r="E4" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F4">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F4" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G4">
+        <v>105</v>
+      </c>
+      <c r="H4">
         <v>100</v>
       </c>
     </row>
@@ -724,12 +736,15 @@
         <v>0</v>
       </c>
       <c r="E5" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F5">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F5" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G5">
+        <v>105</v>
+      </c>
+      <c r="H5">
         <v>100</v>
       </c>
     </row>
@@ -747,12 +762,15 @@
         <v>0</v>
       </c>
       <c r="E6" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F6">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F6" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G6">
+        <v>105</v>
+      </c>
+      <c r="H6">
         <v>100</v>
       </c>
     </row>
@@ -770,12 +788,15 @@
         <v>0</v>
       </c>
       <c r="E7" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F7">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F7" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G7">
+        <v>105</v>
+      </c>
+      <c r="H7">
         <v>100</v>
       </c>
     </row>
@@ -793,12 +814,15 @@
         <v>0</v>
       </c>
       <c r="E8" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F8">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F8" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G8">
+        <v>105</v>
+      </c>
+      <c r="H8">
         <v>100</v>
       </c>
     </row>
@@ -816,12 +840,15 @@
         <v>0</v>
       </c>
       <c r="E9" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F9">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F9" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G9">
+        <v>105</v>
+      </c>
+      <c r="H9">
         <v>100</v>
       </c>
     </row>
@@ -839,12 +866,15 @@
         <v>0</v>
       </c>
       <c r="E10" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F10">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F10" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G10">
+        <v>105</v>
+      </c>
+      <c r="H10">
         <v>100</v>
       </c>
     </row>
@@ -862,12 +892,15 @@
         <v>0</v>
       </c>
       <c r="E11" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F11">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F11" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G11">
+        <v>105</v>
+      </c>
+      <c r="H11">
         <v>100</v>
       </c>
     </row>
@@ -885,12 +918,15 @@
         <v>0</v>
       </c>
       <c r="E12" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F12">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F12" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G12">
+        <v>105</v>
+      </c>
+      <c r="H12">
         <v>100</v>
       </c>
     </row>
@@ -908,12 +944,15 @@
         <v>0</v>
       </c>
       <c r="E13" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F13">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F13" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G13">
+        <v>105</v>
+      </c>
+      <c r="H13">
         <v>100</v>
       </c>
     </row>
@@ -931,12 +970,15 @@
         <v>0</v>
       </c>
       <c r="E14" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F14">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F14" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G14">
+        <v>105</v>
+      </c>
+      <c r="H14">
         <v>100</v>
       </c>
     </row>
@@ -954,12 +996,15 @@
         <v>0</v>
       </c>
       <c r="E15" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F15">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F15" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G15">
+        <v>105</v>
+      </c>
+      <c r="H15">
         <v>100</v>
       </c>
     </row>
@@ -977,12 +1022,15 @@
         <v>0</v>
       </c>
       <c r="E16" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F16">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F16" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G16">
+        <v>105</v>
+      </c>
+      <c r="H16">
         <v>100</v>
       </c>
     </row>
@@ -1000,12 +1048,15 @@
         <v>0</v>
       </c>
       <c r="E17" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F17">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F17" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G17">
+        <v>105</v>
+      </c>
+      <c r="H17">
         <v>100</v>
       </c>
     </row>
@@ -1023,12 +1074,15 @@
         <v>0</v>
       </c>
       <c r="E18" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F18">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F18" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G18">
+        <v>105</v>
+      </c>
+      <c r="H18">
         <v>100</v>
       </c>
     </row>
@@ -1046,12 +1100,15 @@
         <v>0</v>
       </c>
       <c r="E19" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F19">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F19" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G19">
+        <v>105</v>
+      </c>
+      <c r="H19">
         <v>100</v>
       </c>
     </row>
@@ -1069,12 +1126,15 @@
         <v>0</v>
       </c>
       <c r="E20" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F20">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F20" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G20">
+        <v>105</v>
+      </c>
+      <c r="H20">
         <v>100</v>
       </c>
     </row>
@@ -1092,12 +1152,15 @@
         <v>0</v>
       </c>
       <c r="E21" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F21">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F21" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G21">
+        <v>105</v>
+      </c>
+      <c r="H21">
         <v>100</v>
       </c>
     </row>
@@ -1115,12 +1178,15 @@
         <v>0</v>
       </c>
       <c r="E22" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F22">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F22" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G22">
+        <v>105</v>
+      </c>
+      <c r="H22">
         <v>100</v>
       </c>
     </row>
@@ -1138,12 +1204,15 @@
         <v>0</v>
       </c>
       <c r="E23" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F23">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F23" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G23">
+        <v>105</v>
+      </c>
+      <c r="H23">
         <v>100</v>
       </c>
     </row>
@@ -1161,12 +1230,15 @@
         <v>0</v>
       </c>
       <c r="E24" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F24">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F24" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G24">
+        <v>105</v>
+      </c>
+      <c r="H24">
         <v>100</v>
       </c>
     </row>
@@ -1184,12 +1256,15 @@
         <v>0</v>
       </c>
       <c r="E25" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F25">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F25" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G25">
+        <v>105</v>
+      </c>
+      <c r="H25">
         <v>100</v>
       </c>
     </row>
@@ -1207,12 +1282,15 @@
         <v>0</v>
       </c>
       <c r="E26" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F26">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F26" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G26">
+        <v>105</v>
+      </c>
+      <c r="H26">
         <v>100</v>
       </c>
     </row>
@@ -1230,12 +1308,15 @@
         <v>0</v>
       </c>
       <c r="E27" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F27">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F27" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G27">
+        <v>105</v>
+      </c>
+      <c r="H27">
         <v>100</v>
       </c>
     </row>
@@ -1253,12 +1334,15 @@
         <v>0</v>
       </c>
       <c r="E28" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F28">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F28" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G28">
+        <v>105</v>
+      </c>
+      <c r="H28">
         <v>100</v>
       </c>
     </row>
@@ -1276,12 +1360,15 @@
         <v>0</v>
       </c>
       <c r="E29" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F29">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F29" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G29">
+        <v>105</v>
+      </c>
+      <c r="H29">
         <v>100</v>
       </c>
     </row>
@@ -1299,12 +1386,15 @@
         <v>0</v>
       </c>
       <c r="E30" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F30">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F30" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G30">
+        <v>105</v>
+      </c>
+      <c r="H30">
         <v>100</v>
       </c>
     </row>
@@ -1322,12 +1412,15 @@
         <v>0</v>
       </c>
       <c r="E31" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F31">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F31" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G31">
+        <v>105</v>
+      </c>
+      <c r="H31">
         <v>100</v>
       </c>
     </row>
@@ -1345,12 +1438,15 @@
         <v>0</v>
       </c>
       <c r="E32" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F32">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F32" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G32">
+        <v>105</v>
+      </c>
+      <c r="H32">
         <v>100</v>
       </c>
     </row>
@@ -1368,12 +1464,15 @@
         <v>0</v>
       </c>
       <c r="E33" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F33">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F33" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G33">
+        <v>105</v>
+      </c>
+      <c r="H33">
         <v>100</v>
       </c>
     </row>
@@ -1391,12 +1490,15 @@
         <v>0</v>
       </c>
       <c r="E34" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F34">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F34" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G34">
+        <v>105</v>
+      </c>
+      <c r="H34">
         <v>100</v>
       </c>
     </row>
@@ -1414,12 +1516,15 @@
         <v>0</v>
       </c>
       <c r="E35" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F35">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F35" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G35">
+        <v>105</v>
+      </c>
+      <c r="H35">
         <v>100</v>
       </c>
     </row>
@@ -1437,12 +1542,15 @@
         <v>0</v>
       </c>
       <c r="E36" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F36">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F36" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G36">
+        <v>105</v>
+      </c>
+      <c r="H36">
         <v>100</v>
       </c>
     </row>
@@ -1460,12 +1568,15 @@
         <v>0</v>
       </c>
       <c r="E37" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F37">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F37" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G37">
+        <v>105</v>
+      </c>
+      <c r="H37">
         <v>100</v>
       </c>
     </row>
@@ -1483,12 +1594,15 @@
         <v>0</v>
       </c>
       <c r="E38" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F38">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F38" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G38">
+        <v>105</v>
+      </c>
+      <c r="H38">
         <v>100</v>
       </c>
     </row>
@@ -1506,12 +1620,15 @@
         <v>0</v>
       </c>
       <c r="E39" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F39">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F39" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G39">
+        <v>105</v>
+      </c>
+      <c r="H39">
         <v>100</v>
       </c>
     </row>
@@ -1529,12 +1646,15 @@
         <v>0</v>
       </c>
       <c r="E40" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F40">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F40" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G40">
+        <v>105</v>
+      </c>
+      <c r="H40">
         <v>100</v>
       </c>
     </row>
@@ -1552,12 +1672,15 @@
         <v>0</v>
       </c>
       <c r="E41" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F41">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F41" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G41">
+        <v>105</v>
+      </c>
+      <c r="H41">
         <v>100</v>
       </c>
     </row>
@@ -1575,12 +1698,15 @@
         <v>0</v>
       </c>
       <c r="E42" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F42">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F42" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G42">
+        <v>105</v>
+      </c>
+      <c r="H42">
         <v>100</v>
       </c>
     </row>
@@ -1598,12 +1724,15 @@
         <v>0</v>
       </c>
       <c r="E43" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F43">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F43" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G43">
+        <v>105</v>
+      </c>
+      <c r="H43">
         <v>100</v>
       </c>
     </row>
@@ -1621,12 +1750,15 @@
         <v>0</v>
       </c>
       <c r="E44" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F44">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F44" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G44">
+        <v>105</v>
+      </c>
+      <c r="H44">
         <v>100</v>
       </c>
     </row>
@@ -1644,12 +1776,15 @@
         <v>0</v>
       </c>
       <c r="E45" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F45">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F45" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G45">
+        <v>105</v>
+      </c>
+      <c r="H45">
         <v>100</v>
       </c>
     </row>
@@ -1667,12 +1802,15 @@
         <v>0</v>
       </c>
       <c r="E46" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F46">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F46" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G46">
+        <v>105</v>
+      </c>
+      <c r="H46">
         <v>100</v>
       </c>
     </row>
@@ -1690,12 +1828,15 @@
         <v>0</v>
       </c>
       <c r="E47" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F47">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F47" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G47">
+        <v>105</v>
+      </c>
+      <c r="H47">
         <v>100</v>
       </c>
     </row>
@@ -1713,12 +1854,15 @@
         <v>0</v>
       </c>
       <c r="E48" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F48">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F48" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G48">
+        <v>105</v>
+      </c>
+      <c r="H48">
         <v>100</v>
       </c>
     </row>
@@ -1736,12 +1880,15 @@
         <v>0</v>
       </c>
       <c r="E49" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F49">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F49" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G49">
+        <v>105</v>
+      </c>
+      <c r="H49">
         <v>100</v>
       </c>
     </row>
@@ -1759,12 +1906,15 @@
         <v>0</v>
       </c>
       <c r="E50" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F50">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F50" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G50">
+        <v>105</v>
+      </c>
+      <c r="H50">
         <v>100</v>
       </c>
     </row>
@@ -1782,12 +1932,15 @@
         <v>0</v>
       </c>
       <c r="E51" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F51">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F51" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G51">
+        <v>105</v>
+      </c>
+      <c r="H51">
         <v>100</v>
       </c>
     </row>
@@ -1805,12 +1958,15 @@
         <v>0</v>
       </c>
       <c r="E52" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F52">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F52" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G52">
+        <v>105</v>
+      </c>
+      <c r="H52">
         <v>100</v>
       </c>
     </row>
@@ -1828,12 +1984,15 @@
         <v>0</v>
       </c>
       <c r="E53" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F53">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F53" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G53">
+        <v>105</v>
+      </c>
+      <c r="H53">
         <v>100</v>
       </c>
     </row>
@@ -1851,12 +2010,15 @@
         <v>0</v>
       </c>
       <c r="E54" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F54">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F54" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G54">
+        <v>105</v>
+      </c>
+      <c r="H54">
         <v>100</v>
       </c>
     </row>
@@ -1874,12 +2036,15 @@
         <v>0</v>
       </c>
       <c r="E55" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F55">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F55" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G55">
+        <v>105</v>
+      </c>
+      <c r="H55">
         <v>100</v>
       </c>
     </row>
@@ -1897,12 +2062,15 @@
         <v>0</v>
       </c>
       <c r="E56" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F56">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F56" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G56">
+        <v>105</v>
+      </c>
+      <c r="H56">
         <v>100</v>
       </c>
     </row>
@@ -1920,12 +2088,15 @@
         <v>0</v>
       </c>
       <c r="E57" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F57">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F57" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G57">
+        <v>105</v>
+      </c>
+      <c r="H57">
         <v>100</v>
       </c>
     </row>
@@ -1943,12 +2114,15 @@
         <v>0</v>
       </c>
       <c r="E58" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F58">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F58" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G58">
+        <v>105</v>
+      </c>
+      <c r="H58">
         <v>100</v>
       </c>
     </row>
@@ -1966,12 +2140,15 @@
         <v>0</v>
       </c>
       <c r="E59" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F59">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F59" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G59">
+        <v>105</v>
+      </c>
+      <c r="H59">
         <v>100</v>
       </c>
     </row>
@@ -1989,12 +2166,15 @@
         <v>0</v>
       </c>
       <c r="E60" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F60">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F60" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G60">
+        <v>105</v>
+      </c>
+      <c r="H60">
         <v>100</v>
       </c>
     </row>
@@ -2012,12 +2192,15 @@
         <v>0</v>
       </c>
       <c r="E61" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F61">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F61" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G61">
+        <v>105</v>
+      </c>
+      <c r="H61">
         <v>100</v>
       </c>
     </row>
@@ -2035,12 +2218,15 @@
         <v>0</v>
       </c>
       <c r="E62" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F62">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F62" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G62">
+        <v>105</v>
+      </c>
+      <c r="H62">
         <v>100</v>
       </c>
     </row>
@@ -2058,12 +2244,15 @@
         <v>0</v>
       </c>
       <c r="E63" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F63">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F63" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G63">
+        <v>105</v>
+      </c>
+      <c r="H63">
         <v>100</v>
       </c>
     </row>
@@ -2081,12 +2270,15 @@
         <v>0</v>
       </c>
       <c r="E64" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F64">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F64" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G64">
+        <v>105</v>
+      </c>
+      <c r="H64">
         <v>100</v>
       </c>
     </row>
@@ -2104,12 +2296,15 @@
         <v>0</v>
       </c>
       <c r="E65" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F65">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F65" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G65">
+        <v>105</v>
+      </c>
+      <c r="H65">
         <v>100</v>
       </c>
     </row>
@@ -2127,12 +2322,15 @@
         <v>0</v>
       </c>
       <c r="E66" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F66">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F66" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G66">
+        <v>105</v>
+      </c>
+      <c r="H66">
         <v>100</v>
       </c>
     </row>
@@ -2150,12 +2348,15 @@
         <v>0</v>
       </c>
       <c r="E67" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F67">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F67" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G67">
+        <v>105</v>
+      </c>
+      <c r="H67">
         <v>100</v>
       </c>
     </row>
@@ -2173,12 +2374,15 @@
         <v>0</v>
       </c>
       <c r="E68" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F68">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F68" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G68">
+        <v>105</v>
+      </c>
+      <c r="H68">
         <v>100</v>
       </c>
     </row>
@@ -2196,12 +2400,15 @@
         <v>0</v>
       </c>
       <c r="E69" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F69">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F69" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G69">
+        <v>105</v>
+      </c>
+      <c r="H69">
         <v>100</v>
       </c>
     </row>
@@ -2219,12 +2426,15 @@
         <v>0</v>
       </c>
       <c r="E70" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F70">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F70" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G70">
+        <v>105</v>
+      </c>
+      <c r="H70">
         <v>100</v>
       </c>
     </row>
@@ -2242,12 +2452,15 @@
         <v>0</v>
       </c>
       <c r="E71" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F71">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F71" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G71">
+        <v>105</v>
+      </c>
+      <c r="H71">
         <v>100</v>
       </c>
     </row>
@@ -2265,12 +2478,15 @@
         <v>0</v>
       </c>
       <c r="E72" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F72">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F72" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G72">
+        <v>105</v>
+      </c>
+      <c r="H72">
         <v>100</v>
       </c>
     </row>
@@ -2288,12 +2504,15 @@
         <v>0</v>
       </c>
       <c r="E73" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F73">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F73" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G73">
+        <v>105</v>
+      </c>
+      <c r="H73">
         <v>100</v>
       </c>
     </row>
@@ -2311,12 +2530,15 @@
         <v>0</v>
       </c>
       <c r="E74" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F74">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F74" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G74">
+        <v>105</v>
+      </c>
+      <c r="H74">
         <v>100</v>
       </c>
     </row>
@@ -2334,12 +2556,15 @@
         <v>0</v>
       </c>
       <c r="E75" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F75">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F75" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G75">
+        <v>105</v>
+      </c>
+      <c r="H75">
         <v>100</v>
       </c>
     </row>
@@ -2357,12 +2582,15 @@
         <v>0</v>
       </c>
       <c r="E76" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F76">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F76" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G76">
+        <v>105</v>
+      </c>
+      <c r="H76">
         <v>100</v>
       </c>
     </row>
@@ -2380,12 +2608,15 @@
         <v>0</v>
       </c>
       <c r="E77" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F77">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F77" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G77">
+        <v>105</v>
+      </c>
+      <c r="H77">
         <v>100</v>
       </c>
     </row>
@@ -2403,12 +2634,15 @@
         <v>0</v>
       </c>
       <c r="E78" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F78">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F78" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G78">
+        <v>105</v>
+      </c>
+      <c r="H78">
         <v>100</v>
       </c>
     </row>
@@ -2426,12 +2660,15 @@
         <v>0</v>
       </c>
       <c r="E79" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F79">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F79" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G79">
+        <v>105</v>
+      </c>
+      <c r="H79">
         <v>100</v>
       </c>
     </row>
@@ -2449,12 +2686,15 @@
         <v>0</v>
       </c>
       <c r="E80" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F80">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F80" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G80">
+        <v>105</v>
+      </c>
+      <c r="H80">
         <v>100</v>
       </c>
     </row>
@@ -2472,12 +2712,15 @@
         <v>0</v>
       </c>
       <c r="E81" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F81">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F81" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G81">
+        <v>105</v>
+      </c>
+      <c r="H81">
         <v>100</v>
       </c>
     </row>
@@ -2495,12 +2738,15 @@
         <v>0</v>
       </c>
       <c r="E82" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F82">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F82" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G82">
+        <v>105</v>
+      </c>
+      <c r="H82">
         <v>100</v>
       </c>
     </row>
@@ -2518,12 +2764,15 @@
         <v>0</v>
       </c>
       <c r="E83" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F83">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F83" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G83">
+        <v>105</v>
+      </c>
+      <c r="H83">
         <v>100</v>
       </c>
     </row>
@@ -2541,12 +2790,15 @@
         <v>0</v>
       </c>
       <c r="E84" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F84">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F84" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G84">
+        <v>105</v>
+      </c>
+      <c r="H84">
         <v>100</v>
       </c>
     </row>
@@ -2564,12 +2816,15 @@
         <v>0</v>
       </c>
       <c r="E85" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F85">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F85" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G85">
+        <v>105</v>
+      </c>
+      <c r="H85">
         <v>100</v>
       </c>
     </row>
@@ -2587,12 +2842,15 @@
         <v>0</v>
       </c>
       <c r="E86" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F86">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F86" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G86">
+        <v>105</v>
+      </c>
+      <c r="H86">
         <v>100</v>
       </c>
     </row>
@@ -2610,12 +2868,15 @@
         <v>0</v>
       </c>
       <c r="E87" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F87">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F87" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G87">
+        <v>105</v>
+      </c>
+      <c r="H87">
         <v>100</v>
       </c>
     </row>
@@ -2633,12 +2894,15 @@
         <v>0</v>
       </c>
       <c r="E88" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F88">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F88" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G88">
+        <v>105</v>
+      </c>
+      <c r="H88">
         <v>100</v>
       </c>
     </row>
@@ -2656,12 +2920,15 @@
         <v>0</v>
       </c>
       <c r="E89" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F89">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F89" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G89">
+        <v>105</v>
+      </c>
+      <c r="H89">
         <v>100</v>
       </c>
     </row>
@@ -2679,12 +2946,15 @@
         <v>0</v>
       </c>
       <c r="E90" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F90">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F90" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G90">
+        <v>105</v>
+      </c>
+      <c r="H90">
         <v>100</v>
       </c>
     </row>
@@ -2702,12 +2972,15 @@
         <v>0</v>
       </c>
       <c r="E91" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F91">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F91" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G91">
+        <v>105</v>
+      </c>
+      <c r="H91">
         <v>100</v>
       </c>
     </row>
@@ -2725,12 +2998,15 @@
         <v>0</v>
       </c>
       <c r="E92" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F92">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F92" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G92">
+        <v>105</v>
+      </c>
+      <c r="H92">
         <v>100</v>
       </c>
     </row>
@@ -2748,12 +3024,15 @@
         <v>0</v>
       </c>
       <c r="E93" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F93">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F93" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G93">
+        <v>105</v>
+      </c>
+      <c r="H93">
         <v>100</v>
       </c>
     </row>
@@ -2771,12 +3050,15 @@
         <v>0</v>
       </c>
       <c r="E94" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F94">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F94" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G94">
+        <v>105</v>
+      </c>
+      <c r="H94">
         <v>100</v>
       </c>
     </row>
@@ -2794,12 +3076,15 @@
         <v>0</v>
       </c>
       <c r="E95" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F95">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F95" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G95">
+        <v>105</v>
+      </c>
+      <c r="H95">
         <v>100</v>
       </c>
     </row>
@@ -2817,12 +3102,15 @@
         <v>0</v>
       </c>
       <c r="E96" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F96">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F96" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G96">
+        <v>105</v>
+      </c>
+      <c r="H96">
         <v>100</v>
       </c>
     </row>
@@ -2840,12 +3128,15 @@
         <v>0</v>
       </c>
       <c r="E97" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F97">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F97" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G97">
+        <v>105</v>
+      </c>
+      <c r="H97">
         <v>100</v>
       </c>
     </row>
@@ -2863,12 +3154,15 @@
         <v>0</v>
       </c>
       <c r="E98" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F98">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F98" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G98">
+        <v>105</v>
+      </c>
+      <c r="H98">
         <v>100</v>
       </c>
     </row>
@@ -2886,12 +3180,15 @@
         <v>0</v>
       </c>
       <c r="E99" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F99">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F99" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G99">
+        <v>105</v>
+      </c>
+      <c r="H99">
         <v>100</v>
       </c>
     </row>
@@ -2909,12 +3206,15 @@
         <v>0</v>
       </c>
       <c r="E100" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F100">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F100" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G100">
+        <v>105</v>
+      </c>
+      <c r="H100">
         <v>100</v>
       </c>
     </row>
@@ -2932,12 +3232,15 @@
         <v>0</v>
       </c>
       <c r="E101" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F101">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F101" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G101">
+        <v>105</v>
+      </c>
+      <c r="H101">
         <v>100</v>
       </c>
     </row>
@@ -2955,12 +3258,15 @@
         <v>0</v>
       </c>
       <c r="E102" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F102">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F102" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G102">
+        <v>105</v>
+      </c>
+      <c r="H102">
         <v>100</v>
       </c>
     </row>
@@ -2978,12 +3284,15 @@
         <v>0</v>
       </c>
       <c r="E103" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F103">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F103" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G103">
+        <v>105</v>
+      </c>
+      <c r="H103">
         <v>100</v>
       </c>
     </row>
@@ -3001,12 +3310,15 @@
         <v>0</v>
       </c>
       <c r="E104" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F104">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F104" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G104">
+        <v>105</v>
+      </c>
+      <c r="H104">
         <v>100</v>
       </c>
     </row>
@@ -3024,12 +3336,15 @@
         <v>0</v>
       </c>
       <c r="E105" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F105">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F105" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G105">
+        <v>105</v>
+      </c>
+      <c r="H105">
         <v>100</v>
       </c>
     </row>
@@ -3047,12 +3362,15 @@
         <v>0</v>
       </c>
       <c r="E106" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F106">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F106" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G106">
+        <v>105</v>
+      </c>
+      <c r="H106">
         <v>100</v>
       </c>
     </row>
@@ -3070,12 +3388,15 @@
         <v>0</v>
       </c>
       <c r="E107" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F107">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F107" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G107">
+        <v>105</v>
+      </c>
+      <c r="H107">
         <v>100</v>
       </c>
     </row>
@@ -3093,12 +3414,15 @@
         <v>0</v>
       </c>
       <c r="E108" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F108">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F108" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G108">
+        <v>105</v>
+      </c>
+      <c r="H108">
         <v>100</v>
       </c>
     </row>
@@ -3116,12 +3440,15 @@
         <v>0</v>
       </c>
       <c r="E109" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F109">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F109" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G109">
+        <v>105</v>
+      </c>
+      <c r="H109">
         <v>100</v>
       </c>
     </row>
@@ -3139,12 +3466,15 @@
         <v>0</v>
       </c>
       <c r="E110" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F110">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F110" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G110">
+        <v>105</v>
+      </c>
+      <c r="H110">
         <v>100</v>
       </c>
     </row>
@@ -3162,12 +3492,15 @@
         <v>0</v>
       </c>
       <c r="E111" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F111">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F111" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G111">
+        <v>105</v>
+      </c>
+      <c r="H111">
         <v>100</v>
       </c>
     </row>
@@ -3185,12 +3518,15 @@
         <v>0</v>
       </c>
       <c r="E112" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F112">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F112" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G112">
+        <v>105</v>
+      </c>
+      <c r="H112">
         <v>100</v>
       </c>
     </row>
@@ -3208,12 +3544,15 @@
         <v>0</v>
       </c>
       <c r="E113" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F113">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F113" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G113">
+        <v>105</v>
+      </c>
+      <c r="H113">
         <v>100</v>
       </c>
     </row>
@@ -3231,12 +3570,15 @@
         <v>0</v>
       </c>
       <c r="E114" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F114">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F114" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G114">
+        <v>105</v>
+      </c>
+      <c r="H114">
         <v>100</v>
       </c>
     </row>
@@ -3254,12 +3596,15 @@
         <v>0</v>
       </c>
       <c r="E115" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F115">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F115" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G115">
+        <v>105</v>
+      </c>
+      <c r="H115">
         <v>100</v>
       </c>
     </row>
@@ -3277,12 +3622,15 @@
         <v>0</v>
       </c>
       <c r="E116" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F116">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F116" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G116">
+        <v>105</v>
+      </c>
+      <c r="H116">
         <v>100</v>
       </c>
     </row>
@@ -3300,12 +3648,15 @@
         <v>0</v>
       </c>
       <c r="E117" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F117">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F117" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G117">
+        <v>105</v>
+      </c>
+      <c r="H117">
         <v>100</v>
       </c>
     </row>
@@ -3323,12 +3674,15 @@
         <v>0</v>
       </c>
       <c r="E118" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F118">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F118" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G118">
+        <v>105</v>
+      </c>
+      <c r="H118">
         <v>100</v>
       </c>
     </row>
@@ -3346,12 +3700,15 @@
         <v>0</v>
       </c>
       <c r="E119" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F119">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F119" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G119">
+        <v>105</v>
+      </c>
+      <c r="H119">
         <v>100</v>
       </c>
     </row>
@@ -3369,12 +3726,15 @@
         <v>0</v>
       </c>
       <c r="E120" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F120">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F120" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G120">
+        <v>105</v>
+      </c>
+      <c r="H120">
         <v>100</v>
       </c>
     </row>
@@ -3392,12 +3752,15 @@
         <v>0</v>
       </c>
       <c r="E121" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F121">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F121" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G121">
+        <v>105</v>
+      </c>
+      <c r="H121">
         <v>100</v>
       </c>
     </row>
@@ -3415,12 +3778,15 @@
         <v>0</v>
       </c>
       <c r="E122" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F122">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F122" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G122">
+        <v>105</v>
+      </c>
+      <c r="H122">
         <v>100</v>
       </c>
     </row>
@@ -3438,12 +3804,15 @@
         <v>0</v>
       </c>
       <c r="E123" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F123">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F123" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G123">
+        <v>105</v>
+      </c>
+      <c r="H123">
         <v>100</v>
       </c>
     </row>
@@ -3461,12 +3830,15 @@
         <v>0</v>
       </c>
       <c r="E124" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F124">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F124" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G124">
+        <v>105</v>
+      </c>
+      <c r="H124">
         <v>100</v>
       </c>
     </row>
@@ -3484,12 +3856,15 @@
         <v>0</v>
       </c>
       <c r="E125" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F125">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F125" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G125">
+        <v>105</v>
+      </c>
+      <c r="H125">
         <v>100</v>
       </c>
     </row>
@@ -3507,12 +3882,15 @@
         <v>0</v>
       </c>
       <c r="E126" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F126">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F126" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G126">
+        <v>105</v>
+      </c>
+      <c r="H126">
         <v>100</v>
       </c>
     </row>
@@ -3530,12 +3908,15 @@
         <v>0</v>
       </c>
       <c r="E127" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F127">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F127" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G127">
+        <v>105</v>
+      </c>
+      <c r="H127">
         <v>100</v>
       </c>
     </row>
@@ -3553,12 +3934,15 @@
         <v>0</v>
       </c>
       <c r="E128" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F128">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F128" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G128">
+        <v>105</v>
+      </c>
+      <c r="H128">
         <v>100</v>
       </c>
     </row>
@@ -3576,12 +3960,15 @@
         <v>0</v>
       </c>
       <c r="E129" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F129">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F129" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G129">
+        <v>105</v>
+      </c>
+      <c r="H129">
         <v>100</v>
       </c>
     </row>
@@ -3599,12 +3986,15 @@
         <v>0</v>
       </c>
       <c r="E130" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F130">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F130" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G130">
+        <v>105</v>
+      </c>
+      <c r="H130">
         <v>100</v>
       </c>
     </row>
@@ -3622,12 +4012,15 @@
         <v>0</v>
       </c>
       <c r="E131" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F131">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F131" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G131">
+        <v>105</v>
+      </c>
+      <c r="H131">
         <v>100</v>
       </c>
     </row>
@@ -3645,12 +4038,15 @@
         <v>0</v>
       </c>
       <c r="E132" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F132">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F132" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G132">
+        <v>105</v>
+      </c>
+      <c r="H132">
         <v>100</v>
       </c>
     </row>
@@ -3668,12 +4064,15 @@
         <v>0</v>
       </c>
       <c r="E133" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F133">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F133" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G133">
+        <v>105</v>
+      </c>
+      <c r="H133">
         <v>100</v>
       </c>
     </row>
@@ -3691,12 +4090,15 @@
         <v>0</v>
       </c>
       <c r="E134" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F134">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F134" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G134">
+        <v>105</v>
+      </c>
+      <c r="H134">
         <v>100</v>
       </c>
     </row>
@@ -3714,12 +4116,15 @@
         <v>0</v>
       </c>
       <c r="E135" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F135">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F135" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G135">
+        <v>105</v>
+      </c>
+      <c r="H135">
         <v>100</v>
       </c>
     </row>
@@ -3737,12 +4142,15 @@
         <v>0</v>
       </c>
       <c r="E136" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F136">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F136" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G136">
+        <v>105</v>
+      </c>
+      <c r="H136">
         <v>100</v>
       </c>
     </row>
@@ -3760,12 +4168,15 @@
         <v>0</v>
       </c>
       <c r="E137" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F137">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F137" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G137">
+        <v>105</v>
+      </c>
+      <c r="H137">
         <v>100</v>
       </c>
     </row>
@@ -3783,12 +4194,15 @@
         <v>0</v>
       </c>
       <c r="E138" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F138">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F138" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G138">
+        <v>105</v>
+      </c>
+      <c r="H138">
         <v>100</v>
       </c>
     </row>
@@ -3806,12 +4220,15 @@
         <v>0</v>
       </c>
       <c r="E139" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F139">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F139" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G139">
+        <v>105</v>
+      </c>
+      <c r="H139">
         <v>100</v>
       </c>
     </row>
@@ -3829,12 +4246,15 @@
         <v>0</v>
       </c>
       <c r="E140" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F140">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F140" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G140">
+        <v>105</v>
+      </c>
+      <c r="H140">
         <v>100</v>
       </c>
     </row>
@@ -3852,12 +4272,15 @@
         <v>0</v>
       </c>
       <c r="E141" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F141">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F141" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G141">
+        <v>105</v>
+      </c>
+      <c r="H141">
         <v>100</v>
       </c>
     </row>
@@ -3875,12 +4298,15 @@
         <v>0</v>
       </c>
       <c r="E142" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F142">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F142" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G142">
+        <v>105</v>
+      </c>
+      <c r="H142">
         <v>100</v>
       </c>
     </row>
@@ -3898,12 +4324,15 @@
         <v>0</v>
       </c>
       <c r="E143" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F143">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F143" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G143">
+        <v>105</v>
+      </c>
+      <c r="H143">
         <v>100</v>
       </c>
     </row>
@@ -3921,12 +4350,15 @@
         <v>0</v>
       </c>
       <c r="E144" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F144">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F144" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G144">
+        <v>105</v>
+      </c>
+      <c r="H144">
         <v>100</v>
       </c>
     </row>
@@ -3944,12 +4376,15 @@
         <v>0</v>
       </c>
       <c r="E145" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F145">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F145" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G145">
+        <v>105</v>
+      </c>
+      <c r="H145">
         <v>100</v>
       </c>
     </row>
@@ -3967,12 +4402,15 @@
         <v>0</v>
       </c>
       <c r="E146" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F146">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F146" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G146">
+        <v>105</v>
+      </c>
+      <c r="H146">
         <v>100</v>
       </c>
     </row>
@@ -3990,12 +4428,15 @@
         <v>0</v>
       </c>
       <c r="E147" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F147">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F147" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G147">
+        <v>105</v>
+      </c>
+      <c r="H147">
         <v>100</v>
       </c>
     </row>
@@ -4013,12 +4454,15 @@
         <v>0</v>
       </c>
       <c r="E148" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F148">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F148" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G148">
+        <v>105</v>
+      </c>
+      <c r="H148">
         <v>100</v>
       </c>
     </row>
@@ -4036,12 +4480,15 @@
         <v>0</v>
       </c>
       <c r="E149" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F149">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F149" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G149">
+        <v>105</v>
+      </c>
+      <c r="H149">
         <v>100</v>
       </c>
     </row>
@@ -4059,12 +4506,15 @@
         <v>0</v>
       </c>
       <c r="E150" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F150">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F150" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G150">
+        <v>105</v>
+      </c>
+      <c r="H150">
         <v>100</v>
       </c>
     </row>
@@ -4082,12 +4532,15 @@
         <v>0</v>
       </c>
       <c r="E151" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F151">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F151" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G151">
+        <v>105</v>
+      </c>
+      <c r="H151">
         <v>100</v>
       </c>
     </row>
@@ -4105,12 +4558,15 @@
         <v>0</v>
       </c>
       <c r="E152" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F152">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F152" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G152">
+        <v>105</v>
+      </c>
+      <c r="H152">
         <v>100</v>
       </c>
     </row>
@@ -4128,12 +4584,15 @@
         <v>0</v>
       </c>
       <c r="E153" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F153">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F153" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G153">
+        <v>105</v>
+      </c>
+      <c r="H153">
         <v>100</v>
       </c>
     </row>
@@ -4151,12 +4610,15 @@
         <v>0</v>
       </c>
       <c r="E154" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F154">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F154" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G154">
+        <v>105</v>
+      </c>
+      <c r="H154">
         <v>100</v>
       </c>
     </row>
@@ -4174,12 +4636,15 @@
         <v>0</v>
       </c>
       <c r="E155" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F155">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F155" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G155">
+        <v>105</v>
+      </c>
+      <c r="H155">
         <v>100</v>
       </c>
     </row>
@@ -4197,12 +4662,15 @@
         <v>0</v>
       </c>
       <c r="E156" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F156">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F156" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G156">
+        <v>105</v>
+      </c>
+      <c r="H156">
         <v>100</v>
       </c>
     </row>
@@ -4220,12 +4688,15 @@
         <v>0</v>
       </c>
       <c r="E157" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F157">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F157" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G157">
+        <v>105</v>
+      </c>
+      <c r="H157">
         <v>100</v>
       </c>
     </row>
@@ -4243,12 +4714,15 @@
         <v>0</v>
       </c>
       <c r="E158" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F158">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F158" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G158">
+        <v>105</v>
+      </c>
+      <c r="H158">
         <v>100</v>
       </c>
     </row>
@@ -4266,12 +4740,15 @@
         <v>0</v>
       </c>
       <c r="E159" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F159">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F159" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G159">
+        <v>105</v>
+      </c>
+      <c r="H159">
         <v>100</v>
       </c>
     </row>
@@ -4289,12 +4766,15 @@
         <v>0</v>
       </c>
       <c r="E160" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F160">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F160" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G160">
+        <v>105</v>
+      </c>
+      <c r="H160">
         <v>100</v>
       </c>
     </row>
@@ -4312,12 +4792,15 @@
         <v>0</v>
       </c>
       <c r="E161" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F161">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F161" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G161">
+        <v>105</v>
+      </c>
+      <c r="H161">
         <v>100</v>
       </c>
     </row>
@@ -4335,12 +4818,15 @@
         <v>0</v>
       </c>
       <c r="E162" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F162">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F162" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G162">
+        <v>105</v>
+      </c>
+      <c r="H162">
         <v>100</v>
       </c>
     </row>
@@ -4358,12 +4844,15 @@
         <v>0</v>
       </c>
       <c r="E163" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F163">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F163" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G163">
+        <v>105</v>
+      </c>
+      <c r="H163">
         <v>100</v>
       </c>
     </row>
@@ -4381,12 +4870,15 @@
         <v>0</v>
       </c>
       <c r="E164" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F164">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F164" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G164">
+        <v>105</v>
+      </c>
+      <c r="H164">
         <v>100</v>
       </c>
     </row>
@@ -4404,12 +4896,15 @@
         <v>0</v>
       </c>
       <c r="E165" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F165">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F165" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G165">
+        <v>105</v>
+      </c>
+      <c r="H165">
         <v>100</v>
       </c>
     </row>
@@ -4427,12 +4922,15 @@
         <v>0</v>
       </c>
       <c r="E166" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F166">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F166" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G166">
+        <v>105</v>
+      </c>
+      <c r="H166">
         <v>100</v>
       </c>
     </row>
@@ -4450,12 +4948,15 @@
         <v>0</v>
       </c>
       <c r="E167" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F167">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F167" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G167">
+        <v>105</v>
+      </c>
+      <c r="H167">
         <v>100</v>
       </c>
     </row>
@@ -4473,12 +4974,15 @@
         <v>0</v>
       </c>
       <c r="E168" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F168">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F168" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G168">
+        <v>105</v>
+      </c>
+      <c r="H168">
         <v>100</v>
       </c>
     </row>
@@ -4496,12 +5000,15 @@
         <v>0</v>
       </c>
       <c r="E169" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F169">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F169" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G169">
+        <v>105</v>
+      </c>
+      <c r="H169">
         <v>100</v>
       </c>
     </row>
@@ -4519,12 +5026,15 @@
         <v>0</v>
       </c>
       <c r="E170" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F170">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F170" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G170">
+        <v>105</v>
+      </c>
+      <c r="H170">
         <v>100</v>
       </c>
     </row>
@@ -4542,12 +5052,15 @@
         <v>0</v>
       </c>
       <c r="E171" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F171">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F171" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G171">
+        <v>105</v>
+      </c>
+      <c r="H171">
         <v>100</v>
       </c>
     </row>
@@ -4565,12 +5078,15 @@
         <v>0</v>
       </c>
       <c r="E172" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F172">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F172" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G172">
+        <v>105</v>
+      </c>
+      <c r="H172">
         <v>100</v>
       </c>
     </row>
@@ -4588,12 +5104,15 @@
         <v>0</v>
       </c>
       <c r="E173" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F173">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F173" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G173">
+        <v>105</v>
+      </c>
+      <c r="H173">
         <v>100</v>
       </c>
     </row>
@@ -4611,12 +5130,15 @@
         <v>0</v>
       </c>
       <c r="E174" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F174">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F174" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G174">
+        <v>105</v>
+      </c>
+      <c r="H174">
         <v>100</v>
       </c>
     </row>
@@ -4634,12 +5156,15 @@
         <v>0</v>
       </c>
       <c r="E175" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F175">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F175" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G175">
+        <v>105</v>
+      </c>
+      <c r="H175">
         <v>100</v>
       </c>
     </row>
@@ -4657,12 +5182,15 @@
         <v>0</v>
       </c>
       <c r="E176" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F176">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F176" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G176">
+        <v>105</v>
+      </c>
+      <c r="H176">
         <v>100</v>
       </c>
     </row>
@@ -4680,12 +5208,15 @@
         <v>0</v>
       </c>
       <c r="E177" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F177">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F177" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G177">
+        <v>105</v>
+      </c>
+      <c r="H177">
         <v>100</v>
       </c>
     </row>
@@ -4703,12 +5234,15 @@
         <v>0</v>
       </c>
       <c r="E178" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F178">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F178" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G178">
+        <v>105</v>
+      </c>
+      <c r="H178">
         <v>100</v>
       </c>
     </row>
@@ -4726,12 +5260,15 @@
         <v>0</v>
       </c>
       <c r="E179" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F179">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F179" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G179">
+        <v>105</v>
+      </c>
+      <c r="H179">
         <v>100</v>
       </c>
     </row>
@@ -4749,12 +5286,15 @@
         <v>0</v>
       </c>
       <c r="E180" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F180">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F180" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G180">
+        <v>105</v>
+      </c>
+      <c r="H180">
         <v>100</v>
       </c>
     </row>
@@ -4772,12 +5312,15 @@
         <v>0</v>
       </c>
       <c r="E181" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F181">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F181" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G181">
+        <v>105</v>
+      </c>
+      <c r="H181">
         <v>100</v>
       </c>
     </row>
@@ -4795,12 +5338,15 @@
         <v>0</v>
       </c>
       <c r="E182" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F182">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F182" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G182">
+        <v>105</v>
+      </c>
+      <c r="H182">
         <v>100</v>
       </c>
     </row>
@@ -4818,12 +5364,15 @@
         <v>0</v>
       </c>
       <c r="E183" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F183">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F183" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G183">
+        <v>105</v>
+      </c>
+      <c r="H183">
         <v>100</v>
       </c>
     </row>
@@ -4841,12 +5390,15 @@
         <v>0</v>
       </c>
       <c r="E184" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F184">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F184" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G184">
+        <v>105</v>
+      </c>
+      <c r="H184">
         <v>100</v>
       </c>
     </row>
@@ -4864,12 +5416,15 @@
         <v>0</v>
       </c>
       <c r="E185" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F185">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F185" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G185">
+        <v>105</v>
+      </c>
+      <c r="H185">
         <v>100</v>
       </c>
     </row>
@@ -4887,12 +5442,15 @@
         <v>0</v>
       </c>
       <c r="E186" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F186">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F186" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G186">
+        <v>105</v>
+      </c>
+      <c r="H186">
         <v>100</v>
       </c>
     </row>
@@ -4910,12 +5468,15 @@
         <v>0</v>
       </c>
       <c r="E187" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F187">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F187" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G187">
+        <v>105</v>
+      </c>
+      <c r="H187">
         <v>100</v>
       </c>
     </row>
@@ -4933,12 +5494,15 @@
         <v>0</v>
       </c>
       <c r="E188" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F188">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F188" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G188">
+        <v>105</v>
+      </c>
+      <c r="H188">
         <v>100</v>
       </c>
     </row>
@@ -4956,12 +5520,15 @@
         <v>0</v>
       </c>
       <c r="E189" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F189">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F189" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G189">
+        <v>105</v>
+      </c>
+      <c r="H189">
         <v>100</v>
       </c>
     </row>
@@ -4979,12 +5546,15 @@
         <v>0</v>
       </c>
       <c r="E190" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F190">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F190" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G190">
+        <v>105</v>
+      </c>
+      <c r="H190">
         <v>100</v>
       </c>
     </row>
@@ -5002,12 +5572,15 @@
         <v>0</v>
       </c>
       <c r="E191" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F191">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F191" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G191">
+        <v>105</v>
+      </c>
+      <c r="H191">
         <v>100</v>
       </c>
     </row>
@@ -5025,12 +5598,15 @@
         <v>0</v>
       </c>
       <c r="E192" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F192">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F192" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G192">
+        <v>105</v>
+      </c>
+      <c r="H192">
         <v>100</v>
       </c>
     </row>
@@ -5048,12 +5624,15 @@
         <v>0</v>
       </c>
       <c r="E193" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F193">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F193" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G193">
+        <v>105</v>
+      </c>
+      <c r="H193">
         <v>100</v>
       </c>
     </row>
@@ -5071,12 +5650,15 @@
         <v>0</v>
       </c>
       <c r="E194" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F194">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F194" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G194">
+        <v>105</v>
+      </c>
+      <c r="H194">
         <v>100</v>
       </c>
     </row>
@@ -5094,12 +5676,15 @@
         <v>0</v>
       </c>
       <c r="E195" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F195">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F195" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G195">
+        <v>105</v>
+      </c>
+      <c r="H195">
         <v>100</v>
       </c>
     </row>
@@ -5117,12 +5702,15 @@
         <v>0</v>
       </c>
       <c r="E196" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F196">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F196" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G196">
+        <v>105</v>
+      </c>
+      <c r="H196">
         <v>100</v>
       </c>
     </row>
@@ -5140,12 +5728,15 @@
         <v>0</v>
       </c>
       <c r="E197" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F197">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F197" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G197">
+        <v>105</v>
+      </c>
+      <c r="H197">
         <v>100</v>
       </c>
     </row>
@@ -5163,12 +5754,15 @@
         <v>0</v>
       </c>
       <c r="E198" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F198">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F198" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G198">
+        <v>105</v>
+      </c>
+      <c r="H198">
         <v>100</v>
       </c>
     </row>
@@ -5186,12 +5780,15 @@
         <v>0</v>
       </c>
       <c r="E199" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F199">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F199" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G199">
+        <v>105</v>
+      </c>
+      <c r="H199">
         <v>100</v>
       </c>
     </row>
@@ -5209,12 +5806,15 @@
         <v>0</v>
       </c>
       <c r="E200" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F200">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F200" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G200">
+        <v>105</v>
+      </c>
+      <c r="H200">
         <v>100</v>
       </c>
     </row>
@@ -5232,12 +5832,15 @@
         <v>0</v>
       </c>
       <c r="E201" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F201">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F201" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G201">
+        <v>105</v>
+      </c>
+      <c r="H201">
         <v>100</v>
       </c>
     </row>
@@ -5255,12 +5858,15 @@
         <v>0</v>
       </c>
       <c r="E202" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F202">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F202" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G202">
+        <v>105</v>
+      </c>
+      <c r="H202">
         <v>100</v>
       </c>
     </row>
@@ -5278,12 +5884,15 @@
         <v>0</v>
       </c>
       <c r="E203" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F203">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F203" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G203">
+        <v>105</v>
+      </c>
+      <c r="H203">
         <v>100</v>
       </c>
     </row>
@@ -5301,12 +5910,15 @@
         <v>0</v>
       </c>
       <c r="E204" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F204">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F204" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G204">
+        <v>105</v>
+      </c>
+      <c r="H204">
         <v>100</v>
       </c>
     </row>
@@ -5324,12 +5936,15 @@
         <v>0</v>
       </c>
       <c r="E205" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F205">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F205" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G205">
+        <v>105</v>
+      </c>
+      <c r="H205">
         <v>100</v>
       </c>
     </row>
@@ -5347,12 +5962,15 @@
         <v>0</v>
       </c>
       <c r="E206" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F206">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F206" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G206">
+        <v>105</v>
+      </c>
+      <c r="H206">
         <v>100</v>
       </c>
     </row>
@@ -5370,12 +5988,15 @@
         <v>0</v>
       </c>
       <c r="E207" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F207">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F207" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G207">
+        <v>105</v>
+      </c>
+      <c r="H207">
         <v>100</v>
       </c>
     </row>
@@ -5393,12 +6014,15 @@
         <v>0</v>
       </c>
       <c r="E208" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F208">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F208" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G208">
+        <v>105</v>
+      </c>
+      <c r="H208">
         <v>100</v>
       </c>
     </row>
@@ -5416,12 +6040,15 @@
         <v>0</v>
       </c>
       <c r="E209" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F209">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F209" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G209">
+        <v>105</v>
+      </c>
+      <c r="H209">
         <v>100</v>
       </c>
     </row>
@@ -5439,12 +6066,15 @@
         <v>0</v>
       </c>
       <c r="E210" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F210">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F210" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G210">
+        <v>105</v>
+      </c>
+      <c r="H210">
         <v>100</v>
       </c>
     </row>
@@ -5462,12 +6092,15 @@
         <v>0</v>
       </c>
       <c r="E211" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F211">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F211" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G211">
+        <v>105</v>
+      </c>
+      <c r="H211">
         <v>100</v>
       </c>
     </row>
@@ -5485,12 +6118,15 @@
         <v>0</v>
       </c>
       <c r="E212" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F212">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F212" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G212">
+        <v>105</v>
+      </c>
+      <c r="H212">
         <v>100</v>
       </c>
     </row>
@@ -5508,12 +6144,15 @@
         <v>0</v>
       </c>
       <c r="E213" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F213">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F213" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G213">
+        <v>105</v>
+      </c>
+      <c r="H213">
         <v>100</v>
       </c>
     </row>
@@ -5531,12 +6170,15 @@
         <v>0</v>
       </c>
       <c r="E214" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F214">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F214" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G214">
+        <v>105</v>
+      </c>
+      <c r="H214">
         <v>100</v>
       </c>
     </row>
@@ -5554,12 +6196,15 @@
         <v>0</v>
       </c>
       <c r="E215" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F215">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F215" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G215">
+        <v>105</v>
+      </c>
+      <c r="H215">
         <v>100</v>
       </c>
     </row>
@@ -5577,12 +6222,15 @@
         <v>0</v>
       </c>
       <c r="E216" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F216">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F216" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G216">
+        <v>105</v>
+      </c>
+      <c r="H216">
         <v>100</v>
       </c>
     </row>
@@ -5600,12 +6248,15 @@
         <v>0</v>
       </c>
       <c r="E217" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F217">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F217" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G217">
+        <v>105</v>
+      </c>
+      <c r="H217">
         <v>100</v>
       </c>
     </row>
@@ -5623,12 +6274,15 @@
         <v>0</v>
       </c>
       <c r="E218" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F218">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F218" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G218">
+        <v>105</v>
+      </c>
+      <c r="H218">
         <v>100</v>
       </c>
     </row>
@@ -5646,12 +6300,15 @@
         <v>0</v>
       </c>
       <c r="E219" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F219">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F219" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G219">
+        <v>105</v>
+      </c>
+      <c r="H219">
         <v>100</v>
       </c>
     </row>
@@ -5669,12 +6326,15 @@
         <v>0</v>
       </c>
       <c r="E220" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F220">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F220" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G220">
+        <v>105</v>
+      </c>
+      <c r="H220">
         <v>100</v>
       </c>
     </row>
@@ -5692,12 +6352,15 @@
         <v>0</v>
       </c>
       <c r="E221" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F221">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F221" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G221">
+        <v>105</v>
+      </c>
+      <c r="H221">
         <v>100</v>
       </c>
     </row>
@@ -5715,12 +6378,15 @@
         <v>0</v>
       </c>
       <c r="E222" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F222">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F222" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G222">
+        <v>105</v>
+      </c>
+      <c r="H222">
         <v>100</v>
       </c>
     </row>
@@ -5738,12 +6404,15 @@
         <v>0</v>
       </c>
       <c r="E223" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F223">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F223" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G223">
+        <v>105</v>
+      </c>
+      <c r="H223">
         <v>100</v>
       </c>
     </row>
@@ -5761,12 +6430,15 @@
         <v>0</v>
       </c>
       <c r="E224" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F224">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F224" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G224">
+        <v>105</v>
+      </c>
+      <c r="H224">
         <v>100</v>
       </c>
     </row>
@@ -5784,12 +6456,15 @@
         <v>0</v>
       </c>
       <c r="E225" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F225">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F225" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G225">
+        <v>105</v>
+      </c>
+      <c r="H225">
         <v>100</v>
       </c>
     </row>
@@ -5807,12 +6482,15 @@
         <v>0</v>
       </c>
       <c r="E226" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F226">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F226" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G226">
+        <v>105</v>
+      </c>
+      <c r="H226">
         <v>100</v>
       </c>
     </row>
@@ -5830,12 +6508,15 @@
         <v>0</v>
       </c>
       <c r="E227" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F227">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F227" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G227">
+        <v>105</v>
+      </c>
+      <c r="H227">
         <v>100</v>
       </c>
     </row>
@@ -5853,12 +6534,15 @@
         <v>0</v>
       </c>
       <c r="E228" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F228">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F228" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G228">
+        <v>105</v>
+      </c>
+      <c r="H228">
         <v>100</v>
       </c>
     </row>
@@ -5876,12 +6560,15 @@
         <v>0</v>
       </c>
       <c r="E229" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F229">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F229" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G229">
+        <v>105</v>
+      </c>
+      <c r="H229">
         <v>100</v>
       </c>
     </row>
@@ -5899,12 +6586,15 @@
         <v>0</v>
       </c>
       <c r="E230" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F230">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F230" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G230">
+        <v>105</v>
+      </c>
+      <c r="H230">
         <v>100</v>
       </c>
     </row>
@@ -5922,12 +6612,15 @@
         <v>0</v>
       </c>
       <c r="E231" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F231">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F231" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G231">
+        <v>105</v>
+      </c>
+      <c r="H231">
         <v>100</v>
       </c>
     </row>
@@ -5945,12 +6638,15 @@
         <v>0</v>
       </c>
       <c r="E232" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F232">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F232" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G232">
+        <v>105</v>
+      </c>
+      <c r="H232">
         <v>100</v>
       </c>
     </row>
@@ -5968,12 +6664,15 @@
         <v>0</v>
       </c>
       <c r="E233" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F233">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F233" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G233">
+        <v>105</v>
+      </c>
+      <c r="H233">
         <v>100</v>
       </c>
     </row>
@@ -5991,12 +6690,15 @@
         <v>0</v>
       </c>
       <c r="E234" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F234">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F234" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G234">
+        <v>105</v>
+      </c>
+      <c r="H234">
         <v>100</v>
       </c>
     </row>
@@ -6014,12 +6716,15 @@
         <v>0</v>
       </c>
       <c r="E235" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F235">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F235" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G235">
+        <v>105</v>
+      </c>
+      <c r="H235">
         <v>100</v>
       </c>
     </row>
@@ -6037,12 +6742,15 @@
         <v>0</v>
       </c>
       <c r="E236" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F236">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F236" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G236">
+        <v>105</v>
+      </c>
+      <c r="H236">
         <v>100</v>
       </c>
     </row>
@@ -6060,12 +6768,15 @@
         <v>0</v>
       </c>
       <c r="E237" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F237">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F237" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G237">
+        <v>105</v>
+      </c>
+      <c r="H237">
         <v>100</v>
       </c>
     </row>
@@ -6083,12 +6794,15 @@
         <v>0</v>
       </c>
       <c r="E238" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F238">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F238" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G238">
+        <v>105</v>
+      </c>
+      <c r="H238">
         <v>100</v>
       </c>
     </row>
@@ -6106,12 +6820,15 @@
         <v>0</v>
       </c>
       <c r="E239" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F239">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F239" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G239">
+        <v>105</v>
+      </c>
+      <c r="H239">
         <v>100</v>
       </c>
     </row>
@@ -6129,12 +6846,15 @@
         <v>0</v>
       </c>
       <c r="E240" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F240">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F240" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G240">
+        <v>105</v>
+      </c>
+      <c r="H240">
         <v>100</v>
       </c>
     </row>
@@ -6152,12 +6872,15 @@
         <v>0</v>
       </c>
       <c r="E241" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F241">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F241" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G241">
+        <v>105</v>
+      </c>
+      <c r="H241">
         <v>100</v>
       </c>
     </row>
@@ -6175,12 +6898,15 @@
         <v>0</v>
       </c>
       <c r="E242" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F242">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F242" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G242">
+        <v>105</v>
+      </c>
+      <c r="H242">
         <v>100</v>
       </c>
     </row>
@@ -6198,12 +6924,15 @@
         <v>0</v>
       </c>
       <c r="E243" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F243">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F243" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G243">
+        <v>105</v>
+      </c>
+      <c r="H243">
         <v>100</v>
       </c>
     </row>
@@ -6221,12 +6950,15 @@
         <v>0</v>
       </c>
       <c r="E244" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F244">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F244" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G244">
+        <v>105</v>
+      </c>
+      <c r="H244">
         <v>100</v>
       </c>
     </row>
@@ -6244,12 +6976,15 @@
         <v>0</v>
       </c>
       <c r="E245" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F245">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F245" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G245">
+        <v>105</v>
+      </c>
+      <c r="H245">
         <v>100</v>
       </c>
     </row>
@@ -6267,12 +7002,15 @@
         <v>0</v>
       </c>
       <c r="E246" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F246">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F246" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G246">
+        <v>105</v>
+      </c>
+      <c r="H246">
         <v>100</v>
       </c>
     </row>
@@ -6290,12 +7028,15 @@
         <v>0</v>
       </c>
       <c r="E247" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F247">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F247" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G247">
+        <v>105</v>
+      </c>
+      <c r="H247">
         <v>100</v>
       </c>
     </row>
@@ -6313,12 +7054,15 @@
         <v>0</v>
       </c>
       <c r="E248" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F248">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F248" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G248">
+        <v>105</v>
+      </c>
+      <c r="H248">
         <v>100</v>
       </c>
     </row>
@@ -6336,12 +7080,15 @@
         <v>0</v>
       </c>
       <c r="E249" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F249">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F249" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G249">
+        <v>105</v>
+      </c>
+      <c r="H249">
         <v>100</v>
       </c>
     </row>
@@ -6359,12 +7106,15 @@
         <v>0</v>
       </c>
       <c r="E250" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F250">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F250" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G250">
+        <v>105</v>
+      </c>
+      <c r="H250">
         <v>100</v>
       </c>
     </row>
@@ -6382,12 +7132,15 @@
         <v>0</v>
       </c>
       <c r="E251" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F251">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F251" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G251">
+        <v>105</v>
+      </c>
+      <c r="H251">
         <v>100</v>
       </c>
     </row>
@@ -6405,12 +7158,15 @@
         <v>0</v>
       </c>
       <c r="E252" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F252">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F252" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G252">
+        <v>105</v>
+      </c>
+      <c r="H252">
         <v>100</v>
       </c>
     </row>
@@ -6428,12 +7184,15 @@
         <v>0</v>
       </c>
       <c r="E253" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F253">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F253" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G253">
+        <v>105</v>
+      </c>
+      <c r="H253">
         <v>100</v>
       </c>
     </row>
@@ -6451,12 +7210,15 @@
         <v>0</v>
       </c>
       <c r="E254" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F254">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F254" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G254">
+        <v>105</v>
+      </c>
+      <c r="H254">
         <v>100</v>
       </c>
     </row>
@@ -6474,12 +7236,15 @@
         <v>0</v>
       </c>
       <c r="E255" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F255">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F255" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G255">
+        <v>105</v>
+      </c>
+      <c r="H255">
         <v>100</v>
       </c>
     </row>
@@ -6497,12 +7262,15 @@
         <v>0</v>
       </c>
       <c r="E256" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F256">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F256" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G256">
+        <v>105</v>
+      </c>
+      <c r="H256">
         <v>100</v>
       </c>
     </row>
@@ -6520,12 +7288,15 @@
         <v>0</v>
       </c>
       <c r="E257" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F257">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F257" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G257">
+        <v>105</v>
+      </c>
+      <c r="H257">
         <v>100</v>
       </c>
     </row>
@@ -6543,12 +7314,15 @@
         <v>0</v>
       </c>
       <c r="E258" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F258">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F258" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G258">
+        <v>105</v>
+      </c>
+      <c r="H258">
         <v>100</v>
       </c>
     </row>
@@ -6566,12 +7340,15 @@
         <v>0</v>
       </c>
       <c r="E259" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F259">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F259" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G259">
+        <v>105</v>
+      </c>
+      <c r="H259">
         <v>100</v>
       </c>
     </row>
@@ -6589,12 +7366,15 @@
         <v>0</v>
       </c>
       <c r="E260" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F260">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F260" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G260">
+        <v>105</v>
+      </c>
+      <c r="H260">
         <v>100</v>
       </c>
     </row>
@@ -6612,12 +7392,15 @@
         <v>0</v>
       </c>
       <c r="E261" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F261">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F261" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G261">
+        <v>105</v>
+      </c>
+      <c r="H261">
         <v>100</v>
       </c>
     </row>
@@ -6635,12 +7418,15 @@
         <v>0</v>
       </c>
       <c r="E262" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F262">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F262" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G262">
+        <v>105</v>
+      </c>
+      <c r="H262">
         <v>100</v>
       </c>
     </row>
@@ -6658,12 +7444,15 @@
         <v>0</v>
       </c>
       <c r="E263" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F263">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F263" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G263">
+        <v>105</v>
+      </c>
+      <c r="H263">
         <v>100</v>
       </c>
     </row>
@@ -6681,12 +7470,15 @@
         <v>0</v>
       </c>
       <c r="E264" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F264">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F264" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G264">
+        <v>105</v>
+      </c>
+      <c r="H264">
         <v>100</v>
       </c>
     </row>
@@ -6704,12 +7496,15 @@
         <v>0</v>
       </c>
       <c r="E265" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F265">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F265" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G265">
+        <v>105</v>
+      </c>
+      <c r="H265">
         <v>100</v>
       </c>
     </row>
@@ -6727,12 +7522,15 @@
         <v>0</v>
       </c>
       <c r="E266" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F266">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F266" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G266">
+        <v>105</v>
+      </c>
+      <c r="H266">
         <v>100</v>
       </c>
     </row>
@@ -6750,12 +7548,15 @@
         <v>0</v>
       </c>
       <c r="E267" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F267">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F267" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G267">
+        <v>105</v>
+      </c>
+      <c r="H267">
         <v>100</v>
       </c>
     </row>
@@ -6773,12 +7574,15 @@
         <v>0</v>
       </c>
       <c r="E268" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F268">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F268" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G268">
+        <v>105</v>
+      </c>
+      <c r="H268">
         <v>100</v>
       </c>
     </row>
@@ -6796,12 +7600,15 @@
         <v>0</v>
       </c>
       <c r="E269" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F269">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F269" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G269">
+        <v>105</v>
+      </c>
+      <c r="H269">
         <v>100</v>
       </c>
     </row>
@@ -6819,12 +7626,15 @@
         <v>0</v>
       </c>
       <c r="E270" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F270">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F270" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G270">
+        <v>105</v>
+      </c>
+      <c r="H270">
         <v>100</v>
       </c>
     </row>
@@ -6842,12 +7652,15 @@
         <v>0</v>
       </c>
       <c r="E271" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F271">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F271" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G271">
+        <v>105</v>
+      </c>
+      <c r="H271">
         <v>100</v>
       </c>
     </row>
@@ -6865,12 +7678,15 @@
         <v>0</v>
       </c>
       <c r="E272" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F272">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F272" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G272">
+        <v>105</v>
+      </c>
+      <c r="H272">
         <v>100</v>
       </c>
     </row>
@@ -6888,12 +7704,15 @@
         <v>0</v>
       </c>
       <c r="E273" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F273">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F273" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G273">
+        <v>105</v>
+      </c>
+      <c r="H273">
         <v>100</v>
       </c>
     </row>
@@ -6911,12 +7730,15 @@
         <v>0</v>
       </c>
       <c r="E274" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F274">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F274" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G274">
+        <v>105</v>
+      </c>
+      <c r="H274">
         <v>100</v>
       </c>
     </row>
@@ -6934,12 +7756,15 @@
         <v>0</v>
       </c>
       <c r="E275" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F275">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F275" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G275">
+        <v>105</v>
+      </c>
+      <c r="H275">
         <v>100</v>
       </c>
     </row>
@@ -6957,12 +7782,15 @@
         <v>0</v>
       </c>
       <c r="E276" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F276">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F276" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G276">
+        <v>105</v>
+      </c>
+      <c r="H276">
         <v>100</v>
       </c>
     </row>
@@ -6980,12 +7808,15 @@
         <v>0</v>
       </c>
       <c r="E277" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F277">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F277" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G277">
+        <v>105</v>
+      </c>
+      <c r="H277">
         <v>100</v>
       </c>
     </row>
@@ -7003,12 +7834,15 @@
         <v>0</v>
       </c>
       <c r="E278" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F278">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F278" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G278">
+        <v>105</v>
+      </c>
+      <c r="H278">
         <v>100</v>
       </c>
     </row>
@@ -7026,12 +7860,15 @@
         <v>0</v>
       </c>
       <c r="E279" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F279">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F279" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G279">
+        <v>105</v>
+      </c>
+      <c r="H279">
         <v>100</v>
       </c>
     </row>
@@ -7049,12 +7886,15 @@
         <v>0</v>
       </c>
       <c r="E280" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F280">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F280" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G280">
+        <v>105</v>
+      </c>
+      <c r="H280">
         <v>100</v>
       </c>
     </row>
@@ -7072,12 +7912,15 @@
         <v>0</v>
       </c>
       <c r="E281" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F281">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F281" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G281">
+        <v>105</v>
+      </c>
+      <c r="H281">
         <v>100</v>
       </c>
     </row>
@@ -7095,12 +7938,15 @@
         <v>0</v>
       </c>
       <c r="E282" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F282">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F282" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G282">
+        <v>105</v>
+      </c>
+      <c r="H282">
         <v>100</v>
       </c>
     </row>
@@ -7118,12 +7964,15 @@
         <v>0</v>
       </c>
       <c r="E283" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F283">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F283" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G283">
+        <v>105</v>
+      </c>
+      <c r="H283">
         <v>100</v>
       </c>
     </row>
@@ -7141,12 +7990,15 @@
         <v>0</v>
       </c>
       <c r="E284" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F284">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F284" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G284">
+        <v>105</v>
+      </c>
+      <c r="H284">
         <v>100</v>
       </c>
     </row>
@@ -7164,12 +8016,15 @@
         <v>0</v>
       </c>
       <c r="E285" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F285">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F285" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G285">
+        <v>105</v>
+      </c>
+      <c r="H285">
         <v>100</v>
       </c>
     </row>
@@ -7187,12 +8042,15 @@
         <v>0</v>
       </c>
       <c r="E286" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F286">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F286" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G286">
+        <v>105</v>
+      </c>
+      <c r="H286">
         <v>100</v>
       </c>
     </row>
@@ -7210,12 +8068,15 @@
         <v>0</v>
       </c>
       <c r="E287" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F287">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F287" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G287">
+        <v>105</v>
+      </c>
+      <c r="H287">
         <v>100</v>
       </c>
     </row>
@@ -7233,12 +8094,15 @@
         <v>0</v>
       </c>
       <c r="E288" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F288">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F288" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G288">
+        <v>105</v>
+      </c>
+      <c r="H288">
         <v>100</v>
       </c>
     </row>
@@ -7256,12 +8120,15 @@
         <v>0</v>
       </c>
       <c r="E289" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F289">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F289" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G289">
+        <v>105</v>
+      </c>
+      <c r="H289">
         <v>100</v>
       </c>
     </row>
@@ -7279,12 +8146,15 @@
         <v>0</v>
       </c>
       <c r="E290" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F290">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F290" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G290">
+        <v>105</v>
+      </c>
+      <c r="H290">
         <v>100</v>
       </c>
     </row>
@@ -7302,12 +8172,15 @@
         <v>0</v>
       </c>
       <c r="E291" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F291">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F291" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G291">
+        <v>105</v>
+      </c>
+      <c r="H291">
         <v>100</v>
       </c>
     </row>
@@ -7325,12 +8198,15 @@
         <v>0</v>
       </c>
       <c r="E292" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F292">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F292" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G292">
+        <v>105</v>
+      </c>
+      <c r="H292">
         <v>100</v>
       </c>
     </row>
@@ -7348,12 +8224,15 @@
         <v>0</v>
       </c>
       <c r="E293" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F293">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F293" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G293">
+        <v>105</v>
+      </c>
+      <c r="H293">
         <v>100</v>
       </c>
     </row>
@@ -7371,12 +8250,15 @@
         <v>0</v>
       </c>
       <c r="E294" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F294">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F294" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G294">
+        <v>105</v>
+      </c>
+      <c r="H294">
         <v>100</v>
       </c>
     </row>
@@ -7394,12 +8276,15 @@
         <v>0</v>
       </c>
       <c r="E295" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F295">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F295" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G295">
+        <v>105</v>
+      </c>
+      <c r="H295">
         <v>100</v>
       </c>
     </row>
@@ -7417,12 +8302,15 @@
         <v>0</v>
       </c>
       <c r="E296" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F296">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F296" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G296">
+        <v>105</v>
+      </c>
+      <c r="H296">
         <v>100</v>
       </c>
     </row>
@@ -7440,12 +8328,15 @@
         <v>0</v>
       </c>
       <c r="E297" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F297">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F297" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G297">
+        <v>105</v>
+      </c>
+      <c r="H297">
         <v>100</v>
       </c>
     </row>
@@ -7463,12 +8354,15 @@
         <v>0</v>
       </c>
       <c r="E298" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F298">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F298" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G298">
+        <v>105</v>
+      </c>
+      <c r="H298">
         <v>100</v>
       </c>
     </row>
@@ -7486,12 +8380,15 @@
         <v>0</v>
       </c>
       <c r="E299" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F299">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F299" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G299">
+        <v>105</v>
+      </c>
+      <c r="H299">
         <v>100</v>
       </c>
     </row>
@@ -7509,12 +8406,15 @@
         <v>0</v>
       </c>
       <c r="E300" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F300">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F300" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G300">
+        <v>105</v>
+      </c>
+      <c r="H300">
         <v>100</v>
       </c>
     </row>
@@ -7532,18 +8432,21 @@
         <v>0</v>
       </c>
       <c r="E301" t="str">
-        <v>200 OK</v>
-      </c>
-      <c r="F301">
-        <v>105</v>
+        <v>Pass</v>
+      </c>
+      <c r="F301" t="str">
+        <v>200 OK</v>
       </c>
       <c r="G301">
+        <v>105</v>
+      </c>
+      <c r="H301">
         <v>100</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G301"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H301"/>
   </ignoredErrors>
 </worksheet>
 </file>